--- a/model/Output_Budget/1. Baseline/Output Files/100000/Output_27_45.xlsx
+++ b/model/Output_Budget/1. Baseline/Output Files/100000/Output_27_45.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2284699.615047774</v>
+        <v>2284734.761426704</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8243774.900860138</v>
+        <v>8248571.364695199</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11352301.47348387</v>
+        <v>11336604.71754492</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4894103.002712198</v>
+        <v>4895069.047112341</v>
       </c>
     </row>
     <row r="11">
@@ -8667,7 +8667,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>149.0459045266863</v>
+        <v>152.0931294520981</v>
       </c>
       <c r="K11" t="n">
         <v>220.0898510449805</v>
@@ -8688,7 +8688,7 @@
         <v>231.2329957552695</v>
       </c>
       <c r="Q11" t="n">
-        <v>190.3056898744495</v>
+        <v>193.3529147998613</v>
       </c>
       <c r="R11" t="n">
         <v>65.71641987298243</v>
@@ -8746,16 +8746,16 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J12" t="n">
-        <v>94.83762666666669</v>
+        <v>97.88485159207848</v>
       </c>
       <c r="K12" t="n">
         <v>137.841438974359</v>
       </c>
       <c r="L12" t="n">
-        <v>138.5543797798742</v>
+        <v>117.2495075551762</v>
       </c>
       <c r="M12" t="n">
-        <v>118.5868641106976</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N12" t="n">
         <v>131.3417120833333</v>
@@ -8764,7 +8764,7 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P12" t="n">
-        <v>101.9744074143302</v>
+        <v>105.021632339742</v>
       </c>
       <c r="Q12" t="n">
         <v>139.9817740860215</v>
@@ -8828,22 +8828,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K13" t="n">
-        <v>97.01325817053538</v>
+        <v>100.0604830959472</v>
       </c>
       <c r="L13" t="n">
-        <v>102.8846762812383</v>
+        <v>105.9319012066501</v>
       </c>
       <c r="M13" t="n">
-        <v>106.9257839476051</v>
+        <v>109.9730088730168</v>
       </c>
       <c r="N13" t="n">
-        <v>95.68554446523319</v>
+        <v>98.73276939064498</v>
       </c>
       <c r="O13" t="n">
-        <v>106.4565384518428</v>
+        <v>109.5037633772546</v>
       </c>
       <c r="P13" t="n">
-        <v>105.7280040491476</v>
+        <v>108.7752289745594</v>
       </c>
       <c r="Q13" t="n">
         <v>65.34295837775146</v>
@@ -8904,7 +8904,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>88.04590452668629</v>
+        <v>87.68672441001351</v>
       </c>
       <c r="K14" t="n">
         <v>220.0898510449805</v>
@@ -8916,7 +8916,7 @@
         <v>230.3462332272727</v>
       </c>
       <c r="N14" t="n">
-        <v>136.4130635965909</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O14" t="n">
         <v>230.0982114216867</v>
@@ -8925,7 +8925,7 @@
         <v>231.2329957552695</v>
       </c>
       <c r="Q14" t="n">
-        <v>129.3056898744495</v>
+        <v>128.9465097577767</v>
       </c>
       <c r="R14" t="n">
         <v>65.71641987298243</v>
@@ -8980,19 +8980,19 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>10.12574714858493</v>
+        <v>6.163199883327223</v>
       </c>
       <c r="J15" t="n">
-        <v>33.83762666666669</v>
+        <v>33.47844654999392</v>
       </c>
       <c r="K15" t="n">
         <v>137.841438974359</v>
       </c>
       <c r="L15" t="n">
-        <v>138.5543797798742</v>
+        <v>45.19519966320141</v>
       </c>
       <c r="M15" t="n">
-        <v>142.1340339220183</v>
+        <v>73.43576930786269</v>
       </c>
       <c r="N15" t="n">
         <v>131.3417120833333</v>
@@ -9001,7 +9001,7 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P15" t="n">
-        <v>40.97440741433024</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q15" t="n">
         <v>139.9817740860215</v>
@@ -9065,25 +9065,25 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K16" t="n">
-        <v>36.01325817053538</v>
+        <v>35.65407805386261</v>
       </c>
       <c r="L16" t="n">
-        <v>134.8846762812383</v>
+        <v>41.52549616456551</v>
       </c>
       <c r="M16" t="n">
-        <v>45.92578394760505</v>
+        <v>45.56660383093228</v>
       </c>
       <c r="N16" t="n">
-        <v>34.68554446523319</v>
+        <v>34.32636434856042</v>
       </c>
       <c r="O16" t="n">
-        <v>45.45653845184279</v>
+        <v>45.09735833517001</v>
       </c>
       <c r="P16" t="n">
-        <v>132.9120554199818</v>
+        <v>44.36882393247484</v>
       </c>
       <c r="Q16" t="n">
-        <v>58.50500162944584</v>
+        <v>58.14582151277307</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -9141,7 +9141,7 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>88.04590452668629</v>
+        <v>87.68672441001351</v>
       </c>
       <c r="K17" t="n">
         <v>220.0898510449805</v>
@@ -9162,7 +9162,7 @@
         <v>231.2329957552695</v>
       </c>
       <c r="Q17" t="n">
-        <v>129.3056898744495</v>
+        <v>128.9465097577767</v>
       </c>
       <c r="R17" t="n">
         <v>65.71641987298243</v>
@@ -9217,16 +9217,16 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>6.522379999999998</v>
+        <v>10.12574714858493</v>
       </c>
       <c r="J18" t="n">
-        <v>33.83762666666669</v>
+        <v>33.47844654999392</v>
       </c>
       <c r="K18" t="n">
-        <v>69.40747671020806</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L18" t="n">
-        <v>138.5543797798742</v>
+        <v>45.19519966320141</v>
       </c>
       <c r="M18" t="n">
         <v>142.1340339220183</v>
@@ -9238,10 +9238,10 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P18" t="n">
-        <v>133.9744074143302</v>
+        <v>40.61522729765747</v>
       </c>
       <c r="Q18" t="n">
-        <v>46.98177408602152</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R18" t="n">
         <v>45.52166981132082</v>
@@ -9299,28 +9299,28 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>33.63624132272336</v>
+        <v>33.63624132272333</v>
       </c>
       <c r="K19" t="n">
-        <v>36.01325817053538</v>
+        <v>35.65407805386261</v>
       </c>
       <c r="L19" t="n">
-        <v>41.88467628123828</v>
+        <v>41.52549616456551</v>
       </c>
       <c r="M19" t="n">
-        <v>45.92578394760505</v>
+        <v>45.56660383093228</v>
       </c>
       <c r="N19" t="n">
-        <v>34.68554446523319</v>
+        <v>70.89348156771992</v>
       </c>
       <c r="O19" t="n">
-        <v>45.45653845184279</v>
+        <v>45.09735833517001</v>
       </c>
       <c r="P19" t="n">
-        <v>44.72800404914761</v>
+        <v>44.36882393247484</v>
       </c>
       <c r="Q19" t="n">
-        <v>58.50500162944584</v>
+        <v>58.14582151277307</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -9378,7 +9378,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>88.04590452668629</v>
+        <v>87.68672441001351</v>
       </c>
       <c r="K20" t="n">
         <v>220.0898510449805</v>
@@ -9399,7 +9399,7 @@
         <v>231.2329957552695</v>
       </c>
       <c r="Q20" t="n">
-        <v>129.3056898744495</v>
+        <v>128.9465097577767</v>
       </c>
       <c r="R20" t="n">
         <v>65.71641987298243</v>
@@ -9454,13 +9454,13 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>6.522379999999998</v>
+        <v>10.12574714858493</v>
       </c>
       <c r="J21" t="n">
-        <v>33.83762666666669</v>
+        <v>33.47844654999392</v>
       </c>
       <c r="K21" t="n">
-        <v>69.40747671020806</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L21" t="n">
         <v>138.5543797798742</v>
@@ -9469,16 +9469,16 @@
         <v>142.1340339220183</v>
       </c>
       <c r="N21" t="n">
-        <v>131.3417120833333</v>
+        <v>37.98253196666053</v>
       </c>
       <c r="O21" t="n">
-        <v>142.5962444444444</v>
+        <v>49.23706432777166</v>
       </c>
       <c r="P21" t="n">
         <v>133.9744074143302</v>
       </c>
       <c r="Q21" t="n">
-        <v>46.98177408602152</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R21" t="n">
         <v>45.52166981132082</v>
@@ -9539,25 +9539,25 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K22" t="n">
-        <v>36.01325817053538</v>
+        <v>35.65407805386261</v>
       </c>
       <c r="L22" t="n">
-        <v>41.88467628123828</v>
+        <v>78.09261338372501</v>
       </c>
       <c r="M22" t="n">
-        <v>45.92578394760505</v>
+        <v>45.56660383093228</v>
       </c>
       <c r="N22" t="n">
-        <v>34.68554446523319</v>
+        <v>34.32636434856042</v>
       </c>
       <c r="O22" t="n">
-        <v>45.45653845184279</v>
+        <v>45.09735833517001</v>
       </c>
       <c r="P22" t="n">
-        <v>44.72800404914761</v>
+        <v>44.36882393247484</v>
       </c>
       <c r="Q22" t="n">
-        <v>58.50500162944584</v>
+        <v>58.14582151277307</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -9615,7 +9615,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>88.04590452668629</v>
+        <v>87.68672441001351</v>
       </c>
       <c r="K23" t="n">
         <v>220.0898510449805</v>
@@ -9636,7 +9636,7 @@
         <v>231.2329957552695</v>
       </c>
       <c r="Q23" t="n">
-        <v>129.3056898744495</v>
+        <v>128.9465097577767</v>
       </c>
       <c r="R23" t="n">
         <v>65.71641987298243</v>
@@ -9691,13 +9691,13 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>6.522379999999998</v>
+        <v>6.163199883327223</v>
       </c>
       <c r="J24" t="n">
-        <v>33.83762666666669</v>
+        <v>33.47844654999392</v>
       </c>
       <c r="K24" t="n">
-        <v>44.84143897435899</v>
+        <v>44.48225885768622</v>
       </c>
       <c r="L24" t="n">
         <v>138.5543797798742</v>
@@ -9706,10 +9706,10 @@
         <v>142.1340339220183</v>
       </c>
       <c r="N24" t="n">
-        <v>131.3417120833333</v>
+        <v>37.98253196666053</v>
       </c>
       <c r="O24" t="n">
-        <v>74.1622821802935</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P24" t="n">
         <v>133.9744074143302</v>
@@ -9776,25 +9776,25 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K25" t="n">
-        <v>36.01325817053538</v>
+        <v>35.65407805386261</v>
       </c>
       <c r="L25" t="n">
-        <v>41.88467628123828</v>
+        <v>41.52549616456551</v>
       </c>
       <c r="M25" t="n">
-        <v>45.92578394760505</v>
+        <v>45.56660383093228</v>
       </c>
       <c r="N25" t="n">
-        <v>34.68554446523319</v>
+        <v>34.32636434856042</v>
       </c>
       <c r="O25" t="n">
-        <v>45.45653845184279</v>
+        <v>45.09735833517001</v>
       </c>
       <c r="P25" t="n">
-        <v>44.72800404914761</v>
+        <v>80.73930445527776</v>
       </c>
       <c r="Q25" t="n">
-        <v>58.50500162944584</v>
+        <v>65.34295837775146</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -9852,7 +9852,7 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>92.04590452668629</v>
+        <v>91.64927167527121</v>
       </c>
       <c r="K26" t="n">
         <v>220.0898510449805</v>
@@ -9873,7 +9873,7 @@
         <v>231.2329957552695</v>
       </c>
       <c r="Q26" t="n">
-        <v>145.8283029397761</v>
+        <v>132.9090570230344</v>
       </c>
       <c r="R26" t="n">
         <v>65.71641987298243</v>
@@ -9931,13 +9931,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J27" t="n">
-        <v>37.83762666666669</v>
+        <v>61.05519871939643</v>
       </c>
       <c r="K27" t="n">
-        <v>48.84143897435899</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L27" t="n">
-        <v>49.55437977987418</v>
+        <v>49.1577469284591</v>
       </c>
       <c r="M27" t="n">
         <v>142.1340339220183</v>
@@ -9946,7 +9946,7 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O27" t="n">
-        <v>142.5962444444444</v>
+        <v>53.19961159302936</v>
       </c>
       <c r="P27" t="n">
         <v>133.9744074143302</v>
@@ -10013,25 +10013,25 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K28" t="n">
-        <v>40.01325817053538</v>
+        <v>39.6166253191203</v>
       </c>
       <c r="L28" t="n">
-        <v>45.88467628123828</v>
+        <v>45.48804342982321</v>
       </c>
       <c r="M28" t="n">
-        <v>49.92578394760505</v>
+        <v>49.52915109618998</v>
       </c>
       <c r="N28" t="n">
-        <v>38.68554446523319</v>
+        <v>38.28891161381812</v>
       </c>
       <c r="O28" t="n">
-        <v>49.45653845184279</v>
+        <v>49.05990560042771</v>
       </c>
       <c r="P28" t="n">
-        <v>48.72800404914761</v>
+        <v>48.33137119773254</v>
       </c>
       <c r="Q28" t="n">
-        <v>62.50500162944584</v>
+        <v>62.10836877803077</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -10089,7 +10089,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>44.04590452668629</v>
+        <v>43.82023248085932</v>
       </c>
       <c r="K29" t="n">
         <v>220.0898510449805</v>
@@ -10110,7 +10110,7 @@
         <v>231.2329957552695</v>
       </c>
       <c r="Q29" t="n">
-        <v>85.30568987444948</v>
+        <v>85.08001782862252</v>
       </c>
       <c r="R29" t="n">
         <v>65.71641987298243</v>
@@ -10171,28 +10171,28 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0.8414389743585957</v>
+        <v>45.18540509978516</v>
       </c>
       <c r="L30" t="n">
-        <v>1.554379779874182</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M30" t="n">
-        <v>5.134033922018318</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>142.5962444444444</v>
+        <v>5.370572398617469</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>139.9817740860215</v>
+        <v>2.756102040194548</v>
       </c>
       <c r="R30" t="n">
-        <v>45.52166981132082</v>
+        <v>8.453831918136984</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -10247,7 +10247,7 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>15.69796098772821</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -10265,10 +10265,10 @@
         <v>138.4565384518428</v>
       </c>
       <c r="P31" t="n">
-        <v>0.7280040491475575</v>
+        <v>0.502332003320646</v>
       </c>
       <c r="Q31" t="n">
-        <v>14.50500162944584</v>
+        <v>14.27932958361887</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -10326,7 +10326,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>44.04590452668629</v>
+        <v>43.82023248085932</v>
       </c>
       <c r="K32" t="n">
         <v>220.0898510449805</v>
@@ -10347,7 +10347,7 @@
         <v>231.2329957552695</v>
       </c>
       <c r="Q32" t="n">
-        <v>85.30568987444948</v>
+        <v>85.08001782862252</v>
       </c>
       <c r="R32" t="n">
         <v>65.71641987298243</v>
@@ -10408,28 +10408,28 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.8414389743589936</v>
+        <v>0.6157669285320253</v>
       </c>
       <c r="L33" t="n">
         <v>138.5543797798742</v>
       </c>
       <c r="M33" t="n">
-        <v>5.134033922018318</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>51.32404858674199</v>
+        <v>5.370572398617469</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>139.9817740860215</v>
+        <v>47.32574021144741</v>
       </c>
       <c r="R33" t="n">
-        <v>8.679503963963953</v>
+        <v>8.453831918136984</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -10502,10 +10502,10 @@
         <v>138.4565384518428</v>
       </c>
       <c r="P34" t="n">
-        <v>0.7280040491475575</v>
+        <v>0.502332003320646</v>
       </c>
       <c r="Q34" t="n">
-        <v>14.50500162944584</v>
+        <v>14.27932958361887</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -10563,7 +10563,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>44.04590452668629</v>
+        <v>43.82023248085932</v>
       </c>
       <c r="K35" t="n">
         <v>220.0898510449805</v>
@@ -10584,7 +10584,7 @@
         <v>231.2329957552695</v>
       </c>
       <c r="Q35" t="n">
-        <v>85.30568987444948</v>
+        <v>85.08001782862252</v>
       </c>
       <c r="R35" t="n">
         <v>65.71641987298243</v>
@@ -10639,34 +10639,34 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>10.12574714858493</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>126.0910353404088</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
         <v>137.841438974359</v>
       </c>
       <c r="L36" t="n">
-        <v>1.554379779874182</v>
+        <v>1.328707734047214</v>
       </c>
       <c r="M36" t="n">
-        <v>5.134033922018318</v>
+        <v>4.90836187619135</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>5.596244444444437</v>
+        <v>5.370572398617469</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>44.56963817125339</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.981774086021517</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R36" t="n">
-        <v>45.52166981132082</v>
+        <v>8.453831918136984</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -10724,7 +10724,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>17.08164525717247</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
         <v>134.8846762812383</v>
@@ -10739,10 +10739,10 @@
         <v>138.4565384518428</v>
       </c>
       <c r="P37" t="n">
-        <v>0.7280040491475575</v>
+        <v>0.502332003320646</v>
       </c>
       <c r="Q37" t="n">
-        <v>14.50500162944584</v>
+        <v>14.27932958361887</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>44.04590452668629</v>
+        <v>43.82023248085932</v>
       </c>
       <c r="K38" t="n">
         <v>220.0898510449805</v>
@@ -10821,7 +10821,7 @@
         <v>231.2329957552695</v>
       </c>
       <c r="Q38" t="n">
-        <v>85.30568987444948</v>
+        <v>85.08001782862252</v>
       </c>
       <c r="R38" t="n">
         <v>65.71641987298243</v>
@@ -10882,28 +10882,28 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0.8414389743589936</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L39" t="n">
-        <v>138.5543797798742</v>
+        <v>1.328707734047214</v>
       </c>
       <c r="M39" t="n">
-        <v>5.134033922018318</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>14.4818829675539</v>
+        <v>5.370572398617469</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>44.56963817125394</v>
       </c>
       <c r="Q39" t="n">
-        <v>139.9817740860215</v>
+        <v>2.756102040194548</v>
       </c>
       <c r="R39" t="n">
-        <v>45.52166981132082</v>
+        <v>8.453831918136984</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -10976,10 +10976,10 @@
         <v>138.4565384518428</v>
       </c>
       <c r="P40" t="n">
-        <v>0.7280040491476143</v>
+        <v>0.502332003320646</v>
       </c>
       <c r="Q40" t="n">
-        <v>14.50500162944584</v>
+        <v>14.27932958361887</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -11037,7 +11037,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>72.04590452668629</v>
+        <v>68.81046029018982</v>
       </c>
       <c r="K41" t="n">
         <v>220.0898510449805</v>
@@ -11058,7 +11058,7 @@
         <v>231.2329957552695</v>
       </c>
       <c r="Q41" t="n">
-        <v>113.3056898744495</v>
+        <v>110.070245637953</v>
       </c>
       <c r="R41" t="n">
         <v>65.71641987298243</v>
@@ -11113,31 +11113,31 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>10.12574714858493</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>98.3920936707249</v>
+        <v>14.60218243017023</v>
       </c>
       <c r="K42" t="n">
         <v>137.841438974359</v>
       </c>
       <c r="L42" t="n">
-        <v>29.55437977987418</v>
+        <v>26.31893554337772</v>
       </c>
       <c r="M42" t="n">
-        <v>33.13403392201832</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N42" t="n">
-        <v>22.34171208333331</v>
+        <v>106.5510377629792</v>
       </c>
       <c r="O42" t="n">
-        <v>33.59624444444444</v>
+        <v>30.36080020794797</v>
       </c>
       <c r="P42" t="n">
-        <v>24.97440741433024</v>
+        <v>21.73896317783378</v>
       </c>
       <c r="Q42" t="n">
-        <v>139.9817740860215</v>
+        <v>27.74632984952505</v>
       </c>
       <c r="R42" t="n">
         <v>45.52166981132082</v>
@@ -11195,10 +11195,10 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>17.99542143939611</v>
+        <v>14.75997720289965</v>
       </c>
       <c r="K43" t="n">
-        <v>20.01325817053538</v>
+        <v>16.77781393403892</v>
       </c>
       <c r="L43" t="n">
         <v>134.8846762812383</v>
@@ -11213,10 +11213,10 @@
         <v>138.4565384518428</v>
       </c>
       <c r="P43" t="n">
-        <v>28.72800404914761</v>
+        <v>25.49255981265115</v>
       </c>
       <c r="Q43" t="n">
-        <v>42.50500162944584</v>
+        <v>39.26955739294938</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -23215,28 +23215,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>350.7338416634806</v>
+        <v>353.7810665888924</v>
       </c>
       <c r="C11" t="n">
-        <v>333.2728917710076</v>
+        <v>336.3201166964193</v>
       </c>
       <c r="D11" t="n">
-        <v>322.683041620683</v>
+        <v>325.7302665460948</v>
       </c>
       <c r="E11" t="n">
-        <v>349.9303700722618</v>
+        <v>352.9775949976736</v>
       </c>
       <c r="F11" t="n">
-        <v>374.8760457417114</v>
+        <v>377.9232706671232</v>
       </c>
       <c r="G11" t="n">
-        <v>383.302737515135</v>
+        <v>386.3499624405468</v>
       </c>
       <c r="H11" t="n">
-        <v>307.4748021157671</v>
+        <v>310.5220270411789</v>
       </c>
       <c r="I11" t="n">
-        <v>178.4758895704059</v>
+        <v>181.5231144958177</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -23263,28 +23263,28 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>117.8691179411497</v>
+        <v>120.9163428665615</v>
       </c>
       <c r="S11" t="n">
-        <v>177.0200695862453</v>
+        <v>180.0672945116571</v>
       </c>
       <c r="T11" t="n">
-        <v>191.0958495641314</v>
+        <v>194.1430744895432</v>
       </c>
       <c r="U11" t="n">
-        <v>219.3456529078365</v>
+        <v>222.3928778332483</v>
       </c>
       <c r="V11" t="n">
-        <v>295.7522584701349</v>
+        <v>298.7994833955467</v>
       </c>
       <c r="W11" t="n">
-        <v>317.240968717413</v>
+        <v>320.2881936428248</v>
       </c>
       <c r="X11" t="n">
-        <v>337.731100678469</v>
+        <v>340.7783256038808</v>
       </c>
       <c r="Y11" t="n">
-        <v>354.2379386560536</v>
+        <v>357.2851635814654</v>
       </c>
     </row>
     <row r="12">
@@ -23294,28 +23294,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>134.5331836498673</v>
+        <v>137.5804085752791</v>
       </c>
       <c r="C12" t="n">
-        <v>140.7084989883157</v>
+        <v>143.7557239137275</v>
       </c>
       <c r="D12" t="n">
-        <v>115.4450655646388</v>
+        <v>118.4922904900505</v>
       </c>
       <c r="E12" t="n">
-        <v>125.6450804554009</v>
+        <v>128.6923053808127</v>
       </c>
       <c r="F12" t="n">
-        <v>113.0692123933839</v>
+        <v>116.1164373187957</v>
       </c>
       <c r="G12" t="n">
-        <v>105.3435171632106</v>
+        <v>108.3907420886224</v>
       </c>
       <c r="H12" t="n">
-        <v>80.23544423649646</v>
+        <v>83.28266916190825</v>
       </c>
       <c r="I12" t="n">
-        <v>57.39663285141508</v>
+        <v>60.44385777682686</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -23342,28 +23342,28 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>68.15783415264313</v>
+        <v>71.20505907805492</v>
       </c>
       <c r="S12" t="n">
-        <v>139.6831711038378</v>
+        <v>142.7303960292496</v>
       </c>
       <c r="T12" t="n">
-        <v>168.1647286948216</v>
+        <v>171.2119536202334</v>
       </c>
       <c r="U12" t="n">
-        <v>193.9413820809748</v>
+        <v>196.9886070063866</v>
       </c>
       <c r="V12" t="n">
-        <v>200.8005871494253</v>
+        <v>203.8478120748371</v>
       </c>
       <c r="W12" t="n">
-        <v>219.6949831609196</v>
+        <v>222.7422080863314</v>
       </c>
       <c r="X12" t="n">
-        <v>173.7729852034775</v>
+        <v>176.8202101288892</v>
       </c>
       <c r="Y12" t="n">
-        <v>173.6826957773044</v>
+        <v>176.7299207027161</v>
       </c>
     </row>
     <row r="13">
@@ -23373,31 +23373,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>147.8319801819373</v>
+        <v>150.8792051073491</v>
       </c>
       <c r="C13" t="n">
-        <v>135.2468210986278</v>
+        <v>138.2940460240396</v>
       </c>
       <c r="D13" t="n">
-        <v>116.6154730182124</v>
+        <v>119.6626979436241</v>
       </c>
       <c r="E13" t="n">
-        <v>114.4339626465692</v>
+        <v>117.481187571981</v>
       </c>
       <c r="F13" t="n">
-        <v>113.4210480229312</v>
+        <v>116.468272948343</v>
       </c>
       <c r="G13" t="n">
-        <v>135.9909793584588</v>
+        <v>139.0382042838705</v>
       </c>
       <c r="H13" t="n">
-        <v>130.2271725074396</v>
+        <v>133.2743974328513</v>
       </c>
       <c r="I13" t="n">
-        <v>123.4504749272583</v>
+        <v>126.4976998526701</v>
       </c>
       <c r="J13" t="n">
-        <v>61.35918011667277</v>
+        <v>64.40640504208456</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -23418,31 +23418,31 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>54.16204325169439</v>
+        <v>57.20926817710617</v>
       </c>
       <c r="R13" t="n">
-        <v>145.2933913771695</v>
+        <v>148.3406163025813</v>
       </c>
       <c r="S13" t="n">
-        <v>192.0165980369723</v>
+        <v>195.0638229623841</v>
       </c>
       <c r="T13" t="n">
-        <v>195.9455894282815</v>
+        <v>198.9928143536933</v>
       </c>
       <c r="U13" t="n">
-        <v>254.3190293564909</v>
+        <v>257.3662542819027</v>
       </c>
       <c r="V13" t="n">
-        <v>220.137643323828</v>
+        <v>223.1848682492398</v>
       </c>
       <c r="W13" t="n">
-        <v>254.522998336591</v>
+        <v>257.5702232620028</v>
       </c>
       <c r="X13" t="n">
-        <v>193.7096553890372</v>
+        <v>196.7568803144489</v>
       </c>
       <c r="Y13" t="n">
-        <v>186.5846533520948</v>
+        <v>189.6318782775066</v>
       </c>
     </row>
     <row r="14">
@@ -23452,28 +23452,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>289.7338416634806</v>
+        <v>289.3746615468078</v>
       </c>
       <c r="C14" t="n">
-        <v>272.2728917710076</v>
+        <v>271.9137116543347</v>
       </c>
       <c r="D14" t="n">
-        <v>261.683041620683</v>
+        <v>261.3238615040102</v>
       </c>
       <c r="E14" t="n">
-        <v>288.9303700722618</v>
+        <v>288.571189955589</v>
       </c>
       <c r="F14" t="n">
-        <v>313.8760457417114</v>
+        <v>313.5168656250387</v>
       </c>
       <c r="G14" t="n">
-        <v>322.302737515135</v>
+        <v>321.9435573984623</v>
       </c>
       <c r="H14" t="n">
-        <v>246.4748021157671</v>
+        <v>246.1156219990944</v>
       </c>
       <c r="I14" t="n">
-        <v>117.4758895704059</v>
+        <v>117.1167094537331</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -23500,28 +23500,28 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>56.86911794114968</v>
+        <v>56.50993782447691</v>
       </c>
       <c r="S14" t="n">
-        <v>116.0200695862453</v>
+        <v>115.6608894695726</v>
       </c>
       <c r="T14" t="n">
-        <v>130.0958495641314</v>
+        <v>129.7366694474586</v>
       </c>
       <c r="U14" t="n">
-        <v>158.3456529078365</v>
+        <v>157.9864727911637</v>
       </c>
       <c r="V14" t="n">
-        <v>234.7522584701349</v>
+        <v>234.3930783534621</v>
       </c>
       <c r="W14" t="n">
-        <v>256.240968717413</v>
+        <v>255.8817886007402</v>
       </c>
       <c r="X14" t="n">
-        <v>276.731100678469</v>
+        <v>276.3719205617963</v>
       </c>
       <c r="Y14" t="n">
-        <v>293.2379386560536</v>
+        <v>292.8787585393808</v>
       </c>
     </row>
     <row r="15">
@@ -23531,25 +23531,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>73.53318364986734</v>
+        <v>73.17400353319456</v>
       </c>
       <c r="C15" t="n">
-        <v>79.70849898831574</v>
+        <v>79.34931887164296</v>
       </c>
       <c r="D15" t="n">
-        <v>54.44506556463875</v>
+        <v>54.08588544796598</v>
       </c>
       <c r="E15" t="n">
-        <v>64.64508045540094</v>
+        <v>64.28590033872817</v>
       </c>
       <c r="F15" t="n">
-        <v>52.06921239338388</v>
+        <v>51.7100322767111</v>
       </c>
       <c r="G15" t="n">
-        <v>44.34351716321063</v>
+        <v>43.98433704653786</v>
       </c>
       <c r="H15" t="n">
-        <v>19.23544423649646</v>
+        <v>18.87626411982369</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -23579,28 +23579,28 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>7.157834152643133</v>
+        <v>6.798654035970358</v>
       </c>
       <c r="S15" t="n">
-        <v>78.68317110383782</v>
+        <v>78.32399098716505</v>
       </c>
       <c r="T15" t="n">
-        <v>107.1647286948216</v>
+        <v>106.8055485781488</v>
       </c>
       <c r="U15" t="n">
-        <v>132.9413820809748</v>
+        <v>132.582201964302</v>
       </c>
       <c r="V15" t="n">
-        <v>139.8005871494253</v>
+        <v>139.4414070327525</v>
       </c>
       <c r="W15" t="n">
-        <v>158.6949831609196</v>
+        <v>158.3358030442468</v>
       </c>
       <c r="X15" t="n">
-        <v>112.7729852034775</v>
+        <v>112.4138050868047</v>
       </c>
       <c r="Y15" t="n">
-        <v>112.6826957773044</v>
+        <v>112.3235156606316</v>
       </c>
     </row>
     <row r="16">
@@ -23610,31 +23610,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>86.8319801819373</v>
+        <v>86.47280006526452</v>
       </c>
       <c r="C16" t="n">
-        <v>74.24682109862783</v>
+        <v>73.88764098195506</v>
       </c>
       <c r="D16" t="n">
-        <v>55.61547301821236</v>
+        <v>55.25629290153958</v>
       </c>
       <c r="E16" t="n">
-        <v>53.43396264656917</v>
+        <v>53.0747825298964</v>
       </c>
       <c r="F16" t="n">
-        <v>52.42104802293125</v>
+        <v>52.06186790625847</v>
       </c>
       <c r="G16" t="n">
-        <v>74.99097935845876</v>
+        <v>74.63179924178598</v>
       </c>
       <c r="H16" t="n">
-        <v>69.22717250743958</v>
+        <v>68.8679923907668</v>
       </c>
       <c r="I16" t="n">
-        <v>62.45047492725828</v>
+        <v>62.09129481058551</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3591801166727606</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -23658,28 +23658,28 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>84.29339137716948</v>
+        <v>83.93421126049671</v>
       </c>
       <c r="S16" t="n">
-        <v>131.0165980369723</v>
+        <v>130.6574179202995</v>
       </c>
       <c r="T16" t="n">
-        <v>134.9455894282815</v>
+        <v>134.5864093116087</v>
       </c>
       <c r="U16" t="n">
-        <v>193.3190293564909</v>
+        <v>192.9598492398181</v>
       </c>
       <c r="V16" t="n">
-        <v>159.137643323828</v>
+        <v>158.7784632071552</v>
       </c>
       <c r="W16" t="n">
-        <v>193.522998336591</v>
+        <v>193.1638182199182</v>
       </c>
       <c r="X16" t="n">
-        <v>132.7096553890372</v>
+        <v>132.3504752723644</v>
       </c>
       <c r="Y16" t="n">
-        <v>125.5846533520948</v>
+        <v>125.225473235422</v>
       </c>
     </row>
     <row r="17">
@@ -23689,28 +23689,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>289.7338416634806</v>
+        <v>289.3746615468078</v>
       </c>
       <c r="C17" t="n">
-        <v>272.2728917710076</v>
+        <v>271.9137116543347</v>
       </c>
       <c r="D17" t="n">
-        <v>261.683041620683</v>
+        <v>261.3238615040102</v>
       </c>
       <c r="E17" t="n">
-        <v>288.9303700722618</v>
+        <v>288.571189955589</v>
       </c>
       <c r="F17" t="n">
-        <v>313.8760457417114</v>
+        <v>313.5168656250387</v>
       </c>
       <c r="G17" t="n">
-        <v>322.302737515135</v>
+        <v>321.9435573984623</v>
       </c>
       <c r="H17" t="n">
-        <v>246.4748021157671</v>
+        <v>246.1156219990944</v>
       </c>
       <c r="I17" t="n">
-        <v>117.4758895704059</v>
+        <v>117.1167094537331</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -23737,28 +23737,28 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>56.86911794114968</v>
+        <v>56.50993782447691</v>
       </c>
       <c r="S17" t="n">
-        <v>116.0200695862453</v>
+        <v>115.6608894695726</v>
       </c>
       <c r="T17" t="n">
-        <v>130.0958495641314</v>
+        <v>129.7366694474586</v>
       </c>
       <c r="U17" t="n">
-        <v>158.3456529078365</v>
+        <v>157.9864727911637</v>
       </c>
       <c r="V17" t="n">
-        <v>234.7522584701349</v>
+        <v>234.3930783534621</v>
       </c>
       <c r="W17" t="n">
-        <v>256.240968717413</v>
+        <v>255.8817886007402</v>
       </c>
       <c r="X17" t="n">
-        <v>276.731100678469</v>
+        <v>276.3719205617963</v>
       </c>
       <c r="Y17" t="n">
-        <v>293.2379386560536</v>
+        <v>292.8787585393808</v>
       </c>
     </row>
     <row r="18">
@@ -23768,25 +23768,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>73.53318364986734</v>
+        <v>73.17400353319456</v>
       </c>
       <c r="C18" t="n">
-        <v>79.70849898831574</v>
+        <v>79.34931887164296</v>
       </c>
       <c r="D18" t="n">
-        <v>54.44506556463875</v>
+        <v>54.08588544796598</v>
       </c>
       <c r="E18" t="n">
-        <v>64.64508045540094</v>
+        <v>64.28590033872817</v>
       </c>
       <c r="F18" t="n">
-        <v>52.06921239338388</v>
+        <v>51.7100322767111</v>
       </c>
       <c r="G18" t="n">
-        <v>44.34351716321063</v>
+        <v>43.98433704653786</v>
       </c>
       <c r="H18" t="n">
-        <v>19.23544423649646</v>
+        <v>18.87626411982369</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -23816,28 +23816,28 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>7.157834152643133</v>
+        <v>6.798654035970358</v>
       </c>
       <c r="S18" t="n">
-        <v>78.68317110383782</v>
+        <v>78.32399098716505</v>
       </c>
       <c r="T18" t="n">
-        <v>107.1647286948216</v>
+        <v>106.8055485781488</v>
       </c>
       <c r="U18" t="n">
-        <v>132.9413820809748</v>
+        <v>132.582201964302</v>
       </c>
       <c r="V18" t="n">
-        <v>139.8005871494253</v>
+        <v>139.4414070327525</v>
       </c>
       <c r="W18" t="n">
-        <v>158.6949831609196</v>
+        <v>158.3358030442468</v>
       </c>
       <c r="X18" t="n">
-        <v>112.7729852034775</v>
+        <v>112.4138050868047</v>
       </c>
       <c r="Y18" t="n">
-        <v>112.6826957773044</v>
+        <v>112.3235156606316</v>
       </c>
     </row>
     <row r="19">
@@ -23847,31 +23847,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>86.8319801819373</v>
+        <v>86.47280006526452</v>
       </c>
       <c r="C19" t="n">
-        <v>74.24682109862783</v>
+        <v>73.88764098195506</v>
       </c>
       <c r="D19" t="n">
-        <v>55.61547301821236</v>
+        <v>55.25629290153958</v>
       </c>
       <c r="E19" t="n">
-        <v>53.43396264656917</v>
+        <v>53.0747825298964</v>
       </c>
       <c r="F19" t="n">
-        <v>52.42104802293125</v>
+        <v>52.06186790625847</v>
       </c>
       <c r="G19" t="n">
-        <v>74.99097935845876</v>
+        <v>74.63179924178598</v>
       </c>
       <c r="H19" t="n">
-        <v>69.22717250743958</v>
+        <v>68.8679923907668</v>
       </c>
       <c r="I19" t="n">
-        <v>62.45047492725828</v>
+        <v>62.09129481058551</v>
       </c>
       <c r="J19" t="n">
-        <v>0.359180116672754</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -23895,28 +23895,28 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>84.29339137716948</v>
+        <v>83.93421126049671</v>
       </c>
       <c r="S19" t="n">
-        <v>131.0165980369723</v>
+        <v>130.6574179202995</v>
       </c>
       <c r="T19" t="n">
-        <v>134.9455894282815</v>
+        <v>134.5864093116087</v>
       </c>
       <c r="U19" t="n">
-        <v>193.3190293564909</v>
+        <v>192.9598492398181</v>
       </c>
       <c r="V19" t="n">
-        <v>159.137643323828</v>
+        <v>158.7784632071552</v>
       </c>
       <c r="W19" t="n">
-        <v>193.522998336591</v>
+        <v>193.1638182199182</v>
       </c>
       <c r="X19" t="n">
-        <v>132.7096553890372</v>
+        <v>132.3504752723644</v>
       </c>
       <c r="Y19" t="n">
-        <v>125.5846533520948</v>
+        <v>125.225473235422</v>
       </c>
     </row>
     <row r="20">
@@ -23926,28 +23926,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>289.7338416634806</v>
+        <v>289.3746615468078</v>
       </c>
       <c r="C20" t="n">
-        <v>272.2728917710076</v>
+        <v>271.9137116543347</v>
       </c>
       <c r="D20" t="n">
-        <v>261.683041620683</v>
+        <v>261.3238615040102</v>
       </c>
       <c r="E20" t="n">
-        <v>288.9303700722618</v>
+        <v>288.571189955589</v>
       </c>
       <c r="F20" t="n">
-        <v>313.8760457417114</v>
+        <v>313.5168656250387</v>
       </c>
       <c r="G20" t="n">
-        <v>322.302737515135</v>
+        <v>321.9435573984623</v>
       </c>
       <c r="H20" t="n">
-        <v>246.4748021157671</v>
+        <v>246.1156219990944</v>
       </c>
       <c r="I20" t="n">
-        <v>117.4758895704059</v>
+        <v>117.1167094537331</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -23974,28 +23974,28 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>56.86911794114968</v>
+        <v>56.50993782447691</v>
       </c>
       <c r="S20" t="n">
-        <v>116.0200695862453</v>
+        <v>115.6608894695726</v>
       </c>
       <c r="T20" t="n">
-        <v>130.0958495641314</v>
+        <v>129.7366694474586</v>
       </c>
       <c r="U20" t="n">
-        <v>158.3456529078365</v>
+        <v>157.9864727911637</v>
       </c>
       <c r="V20" t="n">
-        <v>234.7522584701349</v>
+        <v>234.3930783534621</v>
       </c>
       <c r="W20" t="n">
-        <v>256.240968717413</v>
+        <v>255.8817886007402</v>
       </c>
       <c r="X20" t="n">
-        <v>276.731100678469</v>
+        <v>276.3719205617963</v>
       </c>
       <c r="Y20" t="n">
-        <v>293.2379386560536</v>
+        <v>292.8787585393808</v>
       </c>
     </row>
     <row r="21">
@@ -24005,25 +24005,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>73.53318364986734</v>
+        <v>73.17400353319456</v>
       </c>
       <c r="C21" t="n">
-        <v>79.70849898831574</v>
+        <v>79.34931887164296</v>
       </c>
       <c r="D21" t="n">
-        <v>54.44506556463875</v>
+        <v>54.08588544796598</v>
       </c>
       <c r="E21" t="n">
-        <v>64.64508045540094</v>
+        <v>64.28590033872817</v>
       </c>
       <c r="F21" t="n">
-        <v>52.06921239338388</v>
+        <v>51.7100322767111</v>
       </c>
       <c r="G21" t="n">
-        <v>44.34351716321063</v>
+        <v>43.98433704653786</v>
       </c>
       <c r="H21" t="n">
-        <v>19.23544423649646</v>
+        <v>18.87626411982369</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -24053,28 +24053,28 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>7.157834152643133</v>
+        <v>6.798654035970358</v>
       </c>
       <c r="S21" t="n">
-        <v>78.68317110383782</v>
+        <v>78.32399098716505</v>
       </c>
       <c r="T21" t="n">
-        <v>107.1647286948216</v>
+        <v>106.8055485781488</v>
       </c>
       <c r="U21" t="n">
-        <v>132.9413820809748</v>
+        <v>132.582201964302</v>
       </c>
       <c r="V21" t="n">
-        <v>139.8005871494253</v>
+        <v>139.4414070327525</v>
       </c>
       <c r="W21" t="n">
-        <v>158.6949831609196</v>
+        <v>158.3358030442468</v>
       </c>
       <c r="X21" t="n">
-        <v>112.7729852034775</v>
+        <v>112.4138050868047</v>
       </c>
       <c r="Y21" t="n">
-        <v>112.6826957773044</v>
+        <v>112.3235156606316</v>
       </c>
     </row>
     <row r="22">
@@ -24084,31 +24084,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>86.8319801819373</v>
+        <v>86.47280006526452</v>
       </c>
       <c r="C22" t="n">
-        <v>74.24682109862783</v>
+        <v>73.88764098195506</v>
       </c>
       <c r="D22" t="n">
-        <v>55.61547301821236</v>
+        <v>55.25629290153958</v>
       </c>
       <c r="E22" t="n">
-        <v>53.43396264656917</v>
+        <v>53.0747825298964</v>
       </c>
       <c r="F22" t="n">
-        <v>52.42104802293125</v>
+        <v>52.06186790625847</v>
       </c>
       <c r="G22" t="n">
-        <v>74.99097935845876</v>
+        <v>74.63179924178598</v>
       </c>
       <c r="H22" t="n">
-        <v>69.22717250743958</v>
+        <v>68.8679923907668</v>
       </c>
       <c r="I22" t="n">
-        <v>62.45047492725828</v>
+        <v>62.09129481058551</v>
       </c>
       <c r="J22" t="n">
-        <v>0.359180116672789</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -24132,28 +24132,28 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>84.29339137716948</v>
+        <v>83.93421126049671</v>
       </c>
       <c r="S22" t="n">
-        <v>131.0165980369723</v>
+        <v>130.6574179202995</v>
       </c>
       <c r="T22" t="n">
-        <v>134.9455894282815</v>
+        <v>134.5864093116087</v>
       </c>
       <c r="U22" t="n">
-        <v>193.3190293564909</v>
+        <v>192.9598492398181</v>
       </c>
       <c r="V22" t="n">
-        <v>159.137643323828</v>
+        <v>158.7784632071552</v>
       </c>
       <c r="W22" t="n">
-        <v>193.522998336591</v>
+        <v>193.1638182199182</v>
       </c>
       <c r="X22" t="n">
-        <v>132.7096553890372</v>
+        <v>132.3504752723644</v>
       </c>
       <c r="Y22" t="n">
-        <v>125.5846533520948</v>
+        <v>125.225473235422</v>
       </c>
     </row>
     <row r="23">
@@ -24163,28 +24163,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>289.7338416634806</v>
+        <v>289.3746615468078</v>
       </c>
       <c r="C23" t="n">
-        <v>272.2728917710076</v>
+        <v>271.9137116543347</v>
       </c>
       <c r="D23" t="n">
-        <v>261.683041620683</v>
+        <v>261.3238615040102</v>
       </c>
       <c r="E23" t="n">
-        <v>288.9303700722618</v>
+        <v>288.571189955589</v>
       </c>
       <c r="F23" t="n">
-        <v>313.8760457417114</v>
+        <v>313.5168656250387</v>
       </c>
       <c r="G23" t="n">
-        <v>322.302737515135</v>
+        <v>321.9435573984623</v>
       </c>
       <c r="H23" t="n">
-        <v>246.4748021157671</v>
+        <v>246.1156219990944</v>
       </c>
       <c r="I23" t="n">
-        <v>117.4758895704059</v>
+        <v>117.1167094537331</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -24211,28 +24211,28 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>56.86911794114968</v>
+        <v>56.50993782447691</v>
       </c>
       <c r="S23" t="n">
-        <v>116.0200695862453</v>
+        <v>115.6608894695726</v>
       </c>
       <c r="T23" t="n">
-        <v>130.0958495641314</v>
+        <v>129.7366694474586</v>
       </c>
       <c r="U23" t="n">
-        <v>158.3456529078365</v>
+        <v>157.9864727911637</v>
       </c>
       <c r="V23" t="n">
-        <v>234.7522584701349</v>
+        <v>234.3930783534621</v>
       </c>
       <c r="W23" t="n">
-        <v>256.240968717413</v>
+        <v>255.8817886007402</v>
       </c>
       <c r="X23" t="n">
-        <v>276.731100678469</v>
+        <v>276.3719205617963</v>
       </c>
       <c r="Y23" t="n">
-        <v>293.2379386560536</v>
+        <v>292.8787585393808</v>
       </c>
     </row>
     <row r="24">
@@ -24242,25 +24242,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>73.53318364986734</v>
+        <v>73.17400353319456</v>
       </c>
       <c r="C24" t="n">
-        <v>79.70849898831574</v>
+        <v>79.34931887164296</v>
       </c>
       <c r="D24" t="n">
-        <v>54.44506556463875</v>
+        <v>54.08588544796598</v>
       </c>
       <c r="E24" t="n">
-        <v>64.64508045540094</v>
+        <v>64.28590033872817</v>
       </c>
       <c r="F24" t="n">
-        <v>52.06921239338388</v>
+        <v>51.7100322767111</v>
       </c>
       <c r="G24" t="n">
-        <v>44.34351716321063</v>
+        <v>43.98433704653786</v>
       </c>
       <c r="H24" t="n">
-        <v>19.23544423649646</v>
+        <v>18.87626411982369</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -24290,28 +24290,28 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>7.157834152643133</v>
+        <v>6.798654035970358</v>
       </c>
       <c r="S24" t="n">
-        <v>78.68317110383782</v>
+        <v>78.32399098716505</v>
       </c>
       <c r="T24" t="n">
-        <v>107.1647286948216</v>
+        <v>106.8055485781488</v>
       </c>
       <c r="U24" t="n">
-        <v>132.9413820809748</v>
+        <v>132.582201964302</v>
       </c>
       <c r="V24" t="n">
-        <v>139.8005871494253</v>
+        <v>139.4414070327525</v>
       </c>
       <c r="W24" t="n">
-        <v>158.6949831609196</v>
+        <v>158.3358030442468</v>
       </c>
       <c r="X24" t="n">
-        <v>112.7729852034775</v>
+        <v>112.4138050868047</v>
       </c>
       <c r="Y24" t="n">
-        <v>112.6826957773044</v>
+        <v>112.3235156606316</v>
       </c>
     </row>
     <row r="25">
@@ -24321,31 +24321,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>86.8319801819373</v>
+        <v>86.47280006526452</v>
       </c>
       <c r="C25" t="n">
-        <v>74.24682109862783</v>
+        <v>73.88764098195506</v>
       </c>
       <c r="D25" t="n">
-        <v>55.61547301821236</v>
+        <v>55.25629290153958</v>
       </c>
       <c r="E25" t="n">
-        <v>53.43396264656917</v>
+        <v>53.0747825298964</v>
       </c>
       <c r="F25" t="n">
-        <v>52.42104802293125</v>
+        <v>52.06186790625847</v>
       </c>
       <c r="G25" t="n">
-        <v>74.99097935845876</v>
+        <v>74.63179924178598</v>
       </c>
       <c r="H25" t="n">
-        <v>69.22717250743958</v>
+        <v>68.8679923907668</v>
       </c>
       <c r="I25" t="n">
-        <v>62.45047492725828</v>
+        <v>62.09129481058551</v>
       </c>
       <c r="J25" t="n">
-        <v>0.3591801166727748</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -24369,28 +24369,28 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>84.29339137716948</v>
+        <v>83.93421126049671</v>
       </c>
       <c r="S25" t="n">
-        <v>131.0165980369723</v>
+        <v>130.6574179202995</v>
       </c>
       <c r="T25" t="n">
-        <v>134.9455894282815</v>
+        <v>134.5864093116087</v>
       </c>
       <c r="U25" t="n">
-        <v>193.3190293564909</v>
+        <v>192.9598492398181</v>
       </c>
       <c r="V25" t="n">
-        <v>159.137643323828</v>
+        <v>158.7784632071552</v>
       </c>
       <c r="W25" t="n">
-        <v>193.522998336591</v>
+        <v>193.1638182199182</v>
       </c>
       <c r="X25" t="n">
-        <v>132.7096553890372</v>
+        <v>132.3504752723644</v>
       </c>
       <c r="Y25" t="n">
-        <v>125.5846533520948</v>
+        <v>125.225473235422</v>
       </c>
     </row>
     <row r="26">
@@ -24400,28 +24400,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>293.7338416634806</v>
+        <v>293.3372088120655</v>
       </c>
       <c r="C26" t="n">
-        <v>276.2728917710076</v>
+        <v>275.8762589195925</v>
       </c>
       <c r="D26" t="n">
-        <v>265.683041620683</v>
+        <v>265.2864087692679</v>
       </c>
       <c r="E26" t="n">
-        <v>292.9303700722618</v>
+        <v>292.5337372208467</v>
       </c>
       <c r="F26" t="n">
-        <v>317.8760457417114</v>
+        <v>317.4794128902964</v>
       </c>
       <c r="G26" t="n">
-        <v>326.302737515135</v>
+        <v>325.90610466372</v>
       </c>
       <c r="H26" t="n">
-        <v>250.4748021157671</v>
+        <v>250.0781692643521</v>
       </c>
       <c r="I26" t="n">
-        <v>121.4758895704059</v>
+        <v>121.0792567189908</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -24448,28 +24448,28 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>60.86911794114968</v>
+        <v>60.4724850897346</v>
       </c>
       <c r="S26" t="n">
-        <v>120.0200695862453</v>
+        <v>119.6234367348303</v>
       </c>
       <c r="T26" t="n">
-        <v>134.0958495641314</v>
+        <v>133.6992167127163</v>
       </c>
       <c r="U26" t="n">
-        <v>162.3456529078365</v>
+        <v>161.9490200564214</v>
       </c>
       <c r="V26" t="n">
-        <v>238.7522584701349</v>
+        <v>238.3556256187198</v>
       </c>
       <c r="W26" t="n">
-        <v>260.240968717413</v>
+        <v>259.8443358659979</v>
       </c>
       <c r="X26" t="n">
-        <v>280.731100678469</v>
+        <v>280.334467827054</v>
       </c>
       <c r="Y26" t="n">
-        <v>297.2379386560536</v>
+        <v>296.8413058046385</v>
       </c>
     </row>
     <row r="27">
@@ -24479,28 +24479,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>77.53318364986734</v>
+        <v>77.13655079845226</v>
       </c>
       <c r="C27" t="n">
-        <v>83.70849898831574</v>
+        <v>83.31186613690066</v>
       </c>
       <c r="D27" t="n">
-        <v>58.44506556463875</v>
+        <v>58.04843271322368</v>
       </c>
       <c r="E27" t="n">
-        <v>68.64508045540094</v>
+        <v>68.24844760398587</v>
       </c>
       <c r="F27" t="n">
-        <v>56.06921239338388</v>
+        <v>55.6725795419688</v>
       </c>
       <c r="G27" t="n">
-        <v>48.34351716321063</v>
+        <v>47.94688431179556</v>
       </c>
       <c r="H27" t="n">
-        <v>23.23544423649646</v>
+        <v>22.83881138508139</v>
       </c>
       <c r="I27" t="n">
-        <v>0.396632851415069</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -24527,28 +24527,28 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>11.15783415264313</v>
+        <v>10.76120130122806</v>
       </c>
       <c r="S27" t="n">
-        <v>82.68317110383782</v>
+        <v>82.28653825242274</v>
       </c>
       <c r="T27" t="n">
-        <v>111.1647286948216</v>
+        <v>110.7680958434065</v>
       </c>
       <c r="U27" t="n">
-        <v>136.9413820809748</v>
+        <v>136.5447492295597</v>
       </c>
       <c r="V27" t="n">
-        <v>143.8005871494253</v>
+        <v>143.4039542980102</v>
       </c>
       <c r="W27" t="n">
-        <v>162.6949831609196</v>
+        <v>162.2983503095045</v>
       </c>
       <c r="X27" t="n">
-        <v>116.7729852034775</v>
+        <v>116.3763523520624</v>
       </c>
       <c r="Y27" t="n">
-        <v>116.6826957773044</v>
+        <v>116.2860629258893</v>
       </c>
     </row>
     <row r="28">
@@ -24558,31 +24558,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>90.8319801819373</v>
+        <v>90.43534733052222</v>
       </c>
       <c r="C28" t="n">
-        <v>78.24682109862783</v>
+        <v>77.85018824721276</v>
       </c>
       <c r="D28" t="n">
-        <v>59.61547301821236</v>
+        <v>59.21884016679728</v>
       </c>
       <c r="E28" t="n">
-        <v>57.43396264656917</v>
+        <v>57.03732979515409</v>
       </c>
       <c r="F28" t="n">
-        <v>56.42104802293125</v>
+        <v>56.02441517151617</v>
       </c>
       <c r="G28" t="n">
-        <v>78.99097935845876</v>
+        <v>78.59434650704368</v>
       </c>
       <c r="H28" t="n">
-        <v>73.22717250743958</v>
+        <v>72.8305396560245</v>
       </c>
       <c r="I28" t="n">
-        <v>66.45047492725828</v>
+        <v>66.05384207584321</v>
       </c>
       <c r="J28" t="n">
-        <v>4.359180116672775</v>
+        <v>3.962547265257697</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -24606,28 +24606,28 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>88.29339137716948</v>
+        <v>87.89675852575441</v>
       </c>
       <c r="S28" t="n">
-        <v>135.0165980369723</v>
+        <v>134.6199651855572</v>
       </c>
       <c r="T28" t="n">
-        <v>138.9455894282815</v>
+        <v>138.5489565768664</v>
       </c>
       <c r="U28" t="n">
-        <v>197.3190293564909</v>
+        <v>196.9223965050758</v>
       </c>
       <c r="V28" t="n">
-        <v>163.137643323828</v>
+        <v>162.7410104724129</v>
       </c>
       <c r="W28" t="n">
-        <v>197.522998336591</v>
+        <v>197.1263654851759</v>
       </c>
       <c r="X28" t="n">
-        <v>136.7096553890372</v>
+        <v>136.3130225376221</v>
       </c>
       <c r="Y28" t="n">
-        <v>129.5846533520948</v>
+        <v>129.1880205006797</v>
       </c>
     </row>
     <row r="29">
@@ -24637,28 +24637,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>245.7338416634806</v>
+        <v>245.5081696176536</v>
       </c>
       <c r="C29" t="n">
-        <v>228.2728917710076</v>
+        <v>228.0472197251806</v>
       </c>
       <c r="D29" t="n">
-        <v>217.683041620683</v>
+        <v>217.457369574856</v>
       </c>
       <c r="E29" t="n">
-        <v>244.9303700722618</v>
+        <v>244.7046980264348</v>
       </c>
       <c r="F29" t="n">
-        <v>269.8760457417114</v>
+        <v>269.6503736958845</v>
       </c>
       <c r="G29" t="n">
-        <v>278.302737515135</v>
+        <v>278.0770654693081</v>
       </c>
       <c r="H29" t="n">
-        <v>202.4748021157671</v>
+        <v>202.2491300699402</v>
       </c>
       <c r="I29" t="n">
-        <v>73.47588957040591</v>
+        <v>73.25021752457894</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -24685,28 +24685,28 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>12.86911794114968</v>
+        <v>12.64344589532271</v>
       </c>
       <c r="S29" t="n">
-        <v>72.02006958624534</v>
+        <v>71.79439754041837</v>
       </c>
       <c r="T29" t="n">
-        <v>86.09584956413136</v>
+        <v>85.87017751830439</v>
       </c>
       <c r="U29" t="n">
-        <v>114.3456529078365</v>
+        <v>114.1199808620095</v>
       </c>
       <c r="V29" t="n">
-        <v>190.7522584701349</v>
+        <v>190.5265864243079</v>
       </c>
       <c r="W29" t="n">
-        <v>212.240968717413</v>
+        <v>212.015296671586</v>
       </c>
       <c r="X29" t="n">
-        <v>232.731100678469</v>
+        <v>232.5054286326421</v>
       </c>
       <c r="Y29" t="n">
-        <v>249.2379386560536</v>
+        <v>249.0122666102266</v>
       </c>
     </row>
     <row r="30">
@@ -24716,22 +24716,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>29.53318364986734</v>
+        <v>29.30751160404037</v>
       </c>
       <c r="C30" t="n">
-        <v>35.70849898831574</v>
+        <v>35.48282694248877</v>
       </c>
       <c r="D30" t="n">
-        <v>10.44506556463875</v>
+        <v>10.21939351881178</v>
       </c>
       <c r="E30" t="n">
-        <v>20.64508045540094</v>
+        <v>20.41940840957398</v>
       </c>
       <c r="F30" t="n">
-        <v>8.069212393383879</v>
+        <v>7.84354034755691</v>
       </c>
       <c r="G30" t="n">
-        <v>0.3435171632106346</v>
+        <v>0.1178451173836663</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -24767,25 +24767,25 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>34.68317110383782</v>
+        <v>34.45749905801085</v>
       </c>
       <c r="T30" t="n">
-        <v>63.1647286948216</v>
+        <v>62.93905664899464</v>
       </c>
       <c r="U30" t="n">
-        <v>88.94138208097482</v>
+        <v>88.71571003514785</v>
       </c>
       <c r="V30" t="n">
-        <v>95.80058714942527</v>
+        <v>95.5749151035983</v>
       </c>
       <c r="W30" t="n">
-        <v>114.6949831609196</v>
+        <v>114.4693111150926</v>
       </c>
       <c r="X30" t="n">
-        <v>68.77298520347748</v>
+        <v>68.54731315765051</v>
       </c>
       <c r="Y30" t="n">
-        <v>68.68269577730436</v>
+        <v>68.45702373147739</v>
       </c>
     </row>
     <row r="31">
@@ -24795,28 +24795,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>42.8319801819373</v>
+        <v>42.60630813611033</v>
       </c>
       <c r="C31" t="n">
-        <v>30.24682109862783</v>
+        <v>30.02114905280087</v>
       </c>
       <c r="D31" t="n">
-        <v>11.61547301821236</v>
+        <v>11.38980097238539</v>
       </c>
       <c r="E31" t="n">
-        <v>9.433962646569171</v>
+        <v>9.208290600742203</v>
       </c>
       <c r="F31" t="n">
-        <v>8.421048022931245</v>
+        <v>8.195375977104277</v>
       </c>
       <c r="G31" t="n">
-        <v>30.99097935845876</v>
+        <v>30.76530731263179</v>
       </c>
       <c r="H31" t="n">
-        <v>25.22717250743958</v>
+        <v>25.00150046161261</v>
       </c>
       <c r="I31" t="n">
-        <v>18.45047492725828</v>
+        <v>18.22480288143132</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -24843,28 +24843,28 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>40.29339137716948</v>
+        <v>40.06771933134252</v>
       </c>
       <c r="S31" t="n">
-        <v>87.01659803697225</v>
+        <v>86.79092599114529</v>
       </c>
       <c r="T31" t="n">
-        <v>90.94558942828149</v>
+        <v>90.71991738245453</v>
       </c>
       <c r="U31" t="n">
-        <v>149.3190293564909</v>
+        <v>149.0933573106639</v>
       </c>
       <c r="V31" t="n">
-        <v>115.137643323828</v>
+        <v>114.911971278001</v>
       </c>
       <c r="W31" t="n">
-        <v>149.522998336591</v>
+        <v>149.297326290764</v>
       </c>
       <c r="X31" t="n">
-        <v>88.70965538903715</v>
+        <v>88.48398334321018</v>
       </c>
       <c r="Y31" t="n">
-        <v>81.58465335209479</v>
+        <v>81.35898130626782</v>
       </c>
     </row>
     <row r="32">
@@ -24874,28 +24874,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>245.7338416634806</v>
+        <v>245.5081696176536</v>
       </c>
       <c r="C32" t="n">
-        <v>228.2728917710076</v>
+        <v>228.0472197251806</v>
       </c>
       <c r="D32" t="n">
-        <v>217.683041620683</v>
+        <v>217.457369574856</v>
       </c>
       <c r="E32" t="n">
-        <v>244.9303700722618</v>
+        <v>244.7046980264348</v>
       </c>
       <c r="F32" t="n">
-        <v>269.8760457417114</v>
+        <v>269.6503736958845</v>
       </c>
       <c r="G32" t="n">
-        <v>278.302737515135</v>
+        <v>278.0770654693081</v>
       </c>
       <c r="H32" t="n">
-        <v>202.4748021157671</v>
+        <v>202.2491300699402</v>
       </c>
       <c r="I32" t="n">
-        <v>73.47588957040591</v>
+        <v>73.25021752457894</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -24922,28 +24922,28 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>12.86911794114968</v>
+        <v>12.64344589532271</v>
       </c>
       <c r="S32" t="n">
-        <v>72.02006958624534</v>
+        <v>71.79439754041837</v>
       </c>
       <c r="T32" t="n">
-        <v>86.09584956413136</v>
+        <v>85.87017751830439</v>
       </c>
       <c r="U32" t="n">
-        <v>114.3456529078365</v>
+        <v>114.1199808620095</v>
       </c>
       <c r="V32" t="n">
-        <v>190.7522584701349</v>
+        <v>190.5265864243079</v>
       </c>
       <c r="W32" t="n">
-        <v>212.240968717413</v>
+        <v>212.015296671586</v>
       </c>
       <c r="X32" t="n">
-        <v>232.731100678469</v>
+        <v>232.5054286326421</v>
       </c>
       <c r="Y32" t="n">
-        <v>249.2379386560536</v>
+        <v>249.0122666102266</v>
       </c>
     </row>
     <row r="33">
@@ -24953,22 +24953,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>29.53318364986734</v>
+        <v>29.30751160404037</v>
       </c>
       <c r="C33" t="n">
-        <v>35.70849898831574</v>
+        <v>35.48282694248877</v>
       </c>
       <c r="D33" t="n">
-        <v>10.44506556463875</v>
+        <v>10.21939351881178</v>
       </c>
       <c r="E33" t="n">
-        <v>20.64508045540094</v>
+        <v>20.41940840957398</v>
       </c>
       <c r="F33" t="n">
-        <v>8.069212393383879</v>
+        <v>7.84354034755691</v>
       </c>
       <c r="G33" t="n">
-        <v>0.3435171632106631</v>
+        <v>0.1178451173836663</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -25004,25 +25004,25 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>34.68317110383782</v>
+        <v>34.45749905801085</v>
       </c>
       <c r="T33" t="n">
-        <v>63.1647286948216</v>
+        <v>62.93905664899464</v>
       </c>
       <c r="U33" t="n">
-        <v>88.94138208097482</v>
+        <v>88.71571003514785</v>
       </c>
       <c r="V33" t="n">
-        <v>95.80058714942527</v>
+        <v>95.5749151035983</v>
       </c>
       <c r="W33" t="n">
-        <v>114.6949831609196</v>
+        <v>114.4693111150926</v>
       </c>
       <c r="X33" t="n">
-        <v>68.77298520347748</v>
+        <v>68.54731315765051</v>
       </c>
       <c r="Y33" t="n">
-        <v>68.68269577730436</v>
+        <v>68.45702373147739</v>
       </c>
     </row>
     <row r="34">
@@ -25032,28 +25032,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>42.8319801819373</v>
+        <v>42.60630813611033</v>
       </c>
       <c r="C34" t="n">
-        <v>30.24682109862783</v>
+        <v>30.02114905280087</v>
       </c>
       <c r="D34" t="n">
-        <v>11.61547301821236</v>
+        <v>11.38980097238539</v>
       </c>
       <c r="E34" t="n">
-        <v>9.433962646569171</v>
+        <v>9.208290600742203</v>
       </c>
       <c r="F34" t="n">
-        <v>8.421048022931245</v>
+        <v>8.195375977104277</v>
       </c>
       <c r="G34" t="n">
-        <v>30.99097935845876</v>
+        <v>30.76530731263179</v>
       </c>
       <c r="H34" t="n">
-        <v>25.22717250743958</v>
+        <v>25.00150046161261</v>
       </c>
       <c r="I34" t="n">
-        <v>18.45047492725828</v>
+        <v>18.22480288143132</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -25080,28 +25080,28 @@
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>40.29339137716948</v>
+        <v>40.06771933134252</v>
       </c>
       <c r="S34" t="n">
-        <v>87.01659803697225</v>
+        <v>86.79092599114529</v>
       </c>
       <c r="T34" t="n">
-        <v>90.94558942828149</v>
+        <v>90.71991738245453</v>
       </c>
       <c r="U34" t="n">
-        <v>149.3190293564909</v>
+        <v>149.0933573106639</v>
       </c>
       <c r="V34" t="n">
-        <v>115.137643323828</v>
+        <v>114.911971278001</v>
       </c>
       <c r="W34" t="n">
-        <v>149.522998336591</v>
+        <v>149.297326290764</v>
       </c>
       <c r="X34" t="n">
-        <v>88.70965538903715</v>
+        <v>88.48398334321018</v>
       </c>
       <c r="Y34" t="n">
-        <v>81.58465335209479</v>
+        <v>81.35898130626782</v>
       </c>
     </row>
     <row r="35">
@@ -25111,28 +25111,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>245.7338416634806</v>
+        <v>245.5081696176536</v>
       </c>
       <c r="C35" t="n">
-        <v>228.2728917710076</v>
+        <v>228.0472197251806</v>
       </c>
       <c r="D35" t="n">
-        <v>217.683041620683</v>
+        <v>217.457369574856</v>
       </c>
       <c r="E35" t="n">
-        <v>244.9303700722618</v>
+        <v>244.7046980264348</v>
       </c>
       <c r="F35" t="n">
-        <v>269.8760457417114</v>
+        <v>269.6503736958845</v>
       </c>
       <c r="G35" t="n">
-        <v>278.302737515135</v>
+        <v>278.0770654693081</v>
       </c>
       <c r="H35" t="n">
-        <v>202.4748021157671</v>
+        <v>202.2491300699402</v>
       </c>
       <c r="I35" t="n">
-        <v>73.47588957040591</v>
+        <v>73.25021752457894</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -25159,28 +25159,28 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>12.86911794114968</v>
+        <v>12.64344589532271</v>
       </c>
       <c r="S35" t="n">
-        <v>72.02006958624534</v>
+        <v>71.79439754041837</v>
       </c>
       <c r="T35" t="n">
-        <v>86.09584956413136</v>
+        <v>85.87017751830439</v>
       </c>
       <c r="U35" t="n">
-        <v>114.3456529078365</v>
+        <v>114.1199808620095</v>
       </c>
       <c r="V35" t="n">
-        <v>190.7522584701349</v>
+        <v>190.5265864243079</v>
       </c>
       <c r="W35" t="n">
-        <v>212.240968717413</v>
+        <v>212.015296671586</v>
       </c>
       <c r="X35" t="n">
-        <v>232.731100678469</v>
+        <v>232.5054286326421</v>
       </c>
       <c r="Y35" t="n">
-        <v>249.2379386560536</v>
+        <v>249.0122666102266</v>
       </c>
     </row>
     <row r="36">
@@ -25190,22 +25190,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>29.53318364986734</v>
+        <v>29.30751160404037</v>
       </c>
       <c r="C36" t="n">
-        <v>35.70849898831574</v>
+        <v>35.48282694248877</v>
       </c>
       <c r="D36" t="n">
-        <v>10.44506556463875</v>
+        <v>10.21939351881178</v>
       </c>
       <c r="E36" t="n">
-        <v>20.64508045540094</v>
+        <v>20.41940840957398</v>
       </c>
       <c r="F36" t="n">
-        <v>8.069212393383879</v>
+        <v>7.84354034755691</v>
       </c>
       <c r="G36" t="n">
-        <v>0.3435171632106631</v>
+        <v>0.1178451173836663</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -25241,25 +25241,25 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>34.68317110383782</v>
+        <v>34.45749905801085</v>
       </c>
       <c r="T36" t="n">
-        <v>63.1647286948216</v>
+        <v>62.93905664899464</v>
       </c>
       <c r="U36" t="n">
-        <v>88.94138208097482</v>
+        <v>88.71571003514785</v>
       </c>
       <c r="V36" t="n">
-        <v>95.80058714942527</v>
+        <v>95.5749151035983</v>
       </c>
       <c r="W36" t="n">
-        <v>114.6949831609196</v>
+        <v>114.4693111150926</v>
       </c>
       <c r="X36" t="n">
-        <v>68.77298520347748</v>
+        <v>68.54731315765051</v>
       </c>
       <c r="Y36" t="n">
-        <v>68.68269577730436</v>
+        <v>68.45702373147739</v>
       </c>
     </row>
     <row r="37">
@@ -25269,28 +25269,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>42.8319801819373</v>
+        <v>42.60630813611033</v>
       </c>
       <c r="C37" t="n">
-        <v>30.24682109862783</v>
+        <v>30.02114905280087</v>
       </c>
       <c r="D37" t="n">
-        <v>11.61547301821236</v>
+        <v>11.38980097238539</v>
       </c>
       <c r="E37" t="n">
-        <v>9.433962646569171</v>
+        <v>9.208290600742203</v>
       </c>
       <c r="F37" t="n">
-        <v>8.421048022931245</v>
+        <v>8.195375977104277</v>
       </c>
       <c r="G37" t="n">
-        <v>30.99097935845876</v>
+        <v>30.76530731263179</v>
       </c>
       <c r="H37" t="n">
-        <v>25.22717250743958</v>
+        <v>25.00150046161261</v>
       </c>
       <c r="I37" t="n">
-        <v>18.45047492725828</v>
+        <v>18.22480288143132</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -25317,28 +25317,28 @@
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>40.29339137716948</v>
+        <v>40.06771933134252</v>
       </c>
       <c r="S37" t="n">
-        <v>87.01659803697225</v>
+        <v>86.79092599114529</v>
       </c>
       <c r="T37" t="n">
-        <v>90.94558942828149</v>
+        <v>90.71991738245453</v>
       </c>
       <c r="U37" t="n">
-        <v>149.3190293564909</v>
+        <v>149.0933573106639</v>
       </c>
       <c r="V37" t="n">
-        <v>115.137643323828</v>
+        <v>114.911971278001</v>
       </c>
       <c r="W37" t="n">
-        <v>149.522998336591</v>
+        <v>149.297326290764</v>
       </c>
       <c r="X37" t="n">
-        <v>88.70965538903715</v>
+        <v>88.48398334321018</v>
       </c>
       <c r="Y37" t="n">
-        <v>81.58465335209479</v>
+        <v>81.35898130626782</v>
       </c>
     </row>
     <row r="38">
@@ -25348,28 +25348,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>245.7338416634806</v>
+        <v>245.5081696176536</v>
       </c>
       <c r="C38" t="n">
-        <v>228.2728917710076</v>
+        <v>228.0472197251806</v>
       </c>
       <c r="D38" t="n">
-        <v>217.683041620683</v>
+        <v>217.457369574856</v>
       </c>
       <c r="E38" t="n">
-        <v>244.9303700722618</v>
+        <v>244.7046980264348</v>
       </c>
       <c r="F38" t="n">
-        <v>269.8760457417114</v>
+        <v>269.6503736958845</v>
       </c>
       <c r="G38" t="n">
-        <v>278.302737515135</v>
+        <v>278.0770654693081</v>
       </c>
       <c r="H38" t="n">
-        <v>202.4748021157671</v>
+        <v>202.2491300699402</v>
       </c>
       <c r="I38" t="n">
-        <v>73.47588957040591</v>
+        <v>73.25021752457894</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -25396,28 +25396,28 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>12.86911794114968</v>
+        <v>12.64344589532271</v>
       </c>
       <c r="S38" t="n">
-        <v>72.02006958624534</v>
+        <v>71.79439754041837</v>
       </c>
       <c r="T38" t="n">
-        <v>86.09584956413136</v>
+        <v>85.87017751830439</v>
       </c>
       <c r="U38" t="n">
-        <v>114.3456529078365</v>
+        <v>114.1199808620095</v>
       </c>
       <c r="V38" t="n">
-        <v>190.7522584701349</v>
+        <v>190.5265864243079</v>
       </c>
       <c r="W38" t="n">
-        <v>212.240968717413</v>
+        <v>212.015296671586</v>
       </c>
       <c r="X38" t="n">
-        <v>232.731100678469</v>
+        <v>232.5054286326421</v>
       </c>
       <c r="Y38" t="n">
-        <v>249.2379386560536</v>
+        <v>249.0122666102266</v>
       </c>
     </row>
     <row r="39">
@@ -25427,22 +25427,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>29.53318364986734</v>
+        <v>29.30751160404037</v>
       </c>
       <c r="C39" t="n">
-        <v>35.70849898831574</v>
+        <v>35.48282694248877</v>
       </c>
       <c r="D39" t="n">
-        <v>10.44506556463875</v>
+        <v>10.21939351881178</v>
       </c>
       <c r="E39" t="n">
-        <v>20.64508045540094</v>
+        <v>20.41940840957398</v>
       </c>
       <c r="F39" t="n">
-        <v>8.069212393383879</v>
+        <v>7.84354034755691</v>
       </c>
       <c r="G39" t="n">
-        <v>0.343516935041464</v>
+        <v>0.1178451173836663</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -25478,25 +25478,25 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>34.68317110383782</v>
+        <v>34.45749905801085</v>
       </c>
       <c r="T39" t="n">
-        <v>63.1647286948216</v>
+        <v>62.93905664899464</v>
       </c>
       <c r="U39" t="n">
-        <v>88.94138208097482</v>
+        <v>88.71571003514785</v>
       </c>
       <c r="V39" t="n">
-        <v>95.80058714942527</v>
+        <v>95.5749151035983</v>
       </c>
       <c r="W39" t="n">
-        <v>114.6949831609196</v>
+        <v>114.4693111150926</v>
       </c>
       <c r="X39" t="n">
-        <v>68.77298520347748</v>
+        <v>68.54731315765051</v>
       </c>
       <c r="Y39" t="n">
-        <v>68.68269577730436</v>
+        <v>68.45702373147739</v>
       </c>
     </row>
     <row r="40">
@@ -25506,28 +25506,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>42.8319801819373</v>
+        <v>42.60630813611033</v>
       </c>
       <c r="C40" t="n">
-        <v>30.24682109862783</v>
+        <v>30.02114905280087</v>
       </c>
       <c r="D40" t="n">
-        <v>11.61547301821236</v>
+        <v>11.38980097238539</v>
       </c>
       <c r="E40" t="n">
-        <v>9.433962646569171</v>
+        <v>9.208290600742203</v>
       </c>
       <c r="F40" t="n">
-        <v>8.421048022931245</v>
+        <v>8.195375977104277</v>
       </c>
       <c r="G40" t="n">
-        <v>30.99097935845876</v>
+        <v>30.76530731263179</v>
       </c>
       <c r="H40" t="n">
-        <v>25.22717250743958</v>
+        <v>25.00150046161261</v>
       </c>
       <c r="I40" t="n">
-        <v>18.45047492725828</v>
+        <v>18.22480288143132</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -25554,28 +25554,28 @@
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>40.29339137716948</v>
+        <v>40.06771933134252</v>
       </c>
       <c r="S40" t="n">
-        <v>87.01659803697225</v>
+        <v>86.79092599114529</v>
       </c>
       <c r="T40" t="n">
-        <v>90.94558942828149</v>
+        <v>90.71991738245453</v>
       </c>
       <c r="U40" t="n">
-        <v>149.3190293564909</v>
+        <v>149.0933573106639</v>
       </c>
       <c r="V40" t="n">
-        <v>115.137643323828</v>
+        <v>114.911971278001</v>
       </c>
       <c r="W40" t="n">
-        <v>149.522998336591</v>
+        <v>149.297326290764</v>
       </c>
       <c r="X40" t="n">
-        <v>88.70965538903715</v>
+        <v>88.48398334321018</v>
       </c>
       <c r="Y40" t="n">
-        <v>81.58465335209479</v>
+        <v>81.35898130626782</v>
       </c>
     </row>
     <row r="41">
@@ -25585,28 +25585,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>273.7338416634806</v>
+        <v>270.4983974269841</v>
       </c>
       <c r="C41" t="n">
-        <v>256.2728917710076</v>
+        <v>253.0374475345111</v>
       </c>
       <c r="D41" t="n">
-        <v>245.683041620683</v>
+        <v>242.4475973841865</v>
       </c>
       <c r="E41" t="n">
-        <v>272.9303700722618</v>
+        <v>269.6949258357653</v>
       </c>
       <c r="F41" t="n">
-        <v>297.8760457417114</v>
+        <v>294.640601505215</v>
       </c>
       <c r="G41" t="n">
-        <v>306.302737515135</v>
+        <v>303.0672932786386</v>
       </c>
       <c r="H41" t="n">
-        <v>230.4748021157671</v>
+        <v>227.2393578792707</v>
       </c>
       <c r="I41" t="n">
-        <v>101.4758895704059</v>
+        <v>98.24044533390945</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -25633,28 +25633,28 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>40.86911794114968</v>
+        <v>37.63367370465322</v>
       </c>
       <c r="S41" t="n">
-        <v>100.0200695862453</v>
+        <v>96.78462534974888</v>
       </c>
       <c r="T41" t="n">
-        <v>114.0958495641314</v>
+        <v>110.8604053276349</v>
       </c>
       <c r="U41" t="n">
-        <v>142.3456529078365</v>
+        <v>139.11020867134</v>
       </c>
       <c r="V41" t="n">
-        <v>218.7522584701349</v>
+        <v>215.5168142336385</v>
       </c>
       <c r="W41" t="n">
-        <v>240.240968717413</v>
+        <v>237.0055244809166</v>
       </c>
       <c r="X41" t="n">
-        <v>260.731100678469</v>
+        <v>257.4956564419726</v>
       </c>
       <c r="Y41" t="n">
-        <v>277.2379386560536</v>
+        <v>274.0024944195571</v>
       </c>
     </row>
     <row r="42">
@@ -25664,25 +25664,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>57.53318364986734</v>
+        <v>54.29773941337088</v>
       </c>
       <c r="C42" t="n">
-        <v>63.70849898831574</v>
+        <v>60.47305475181928</v>
       </c>
       <c r="D42" t="n">
-        <v>38.44506556463875</v>
+        <v>35.20962132814229</v>
       </c>
       <c r="E42" t="n">
-        <v>48.64508045540094</v>
+        <v>45.40963621890448</v>
       </c>
       <c r="F42" t="n">
-        <v>36.06921239338388</v>
+        <v>32.83376815688742</v>
       </c>
       <c r="G42" t="n">
-        <v>28.34351716321063</v>
+        <v>25.10807292671417</v>
       </c>
       <c r="H42" t="n">
-        <v>3.235444236496463</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -25715,25 +25715,25 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>62.68317110383782</v>
+        <v>59.44772686734136</v>
       </c>
       <c r="T42" t="n">
-        <v>91.1647286948216</v>
+        <v>87.92928445832514</v>
       </c>
       <c r="U42" t="n">
-        <v>116.9413820809748</v>
+        <v>113.7059378444784</v>
       </c>
       <c r="V42" t="n">
-        <v>123.8005871494253</v>
+        <v>120.5651429129288</v>
       </c>
       <c r="W42" t="n">
-        <v>142.6949831609196</v>
+        <v>139.4595389244232</v>
       </c>
       <c r="X42" t="n">
-        <v>96.77298520347748</v>
+        <v>93.53754096698101</v>
       </c>
       <c r="Y42" t="n">
-        <v>96.68269577730436</v>
+        <v>93.4472515408079</v>
       </c>
     </row>
     <row r="43">
@@ -25743,28 +25743,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>70.8319801819373</v>
+        <v>67.59653594544083</v>
       </c>
       <c r="C43" t="n">
-        <v>58.24682109862783</v>
+        <v>55.01137686213137</v>
       </c>
       <c r="D43" t="n">
-        <v>39.61547301821236</v>
+        <v>36.38002878171589</v>
       </c>
       <c r="E43" t="n">
-        <v>37.43396264656917</v>
+        <v>34.19851841007271</v>
       </c>
       <c r="F43" t="n">
-        <v>36.42104802293125</v>
+        <v>33.18560378643478</v>
       </c>
       <c r="G43" t="n">
-        <v>58.99097935845876</v>
+        <v>55.7555351219623</v>
       </c>
       <c r="H43" t="n">
-        <v>53.22717250743958</v>
+        <v>49.99172827094311</v>
       </c>
       <c r="I43" t="n">
-        <v>46.45047492725828</v>
+        <v>43.21503069076182</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -25791,28 +25791,28 @@
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>68.29339137716948</v>
+        <v>65.05794714067302</v>
       </c>
       <c r="S43" t="n">
-        <v>115.0165980369723</v>
+        <v>111.7811538004758</v>
       </c>
       <c r="T43" t="n">
-        <v>118.9455894282815</v>
+        <v>115.710145191785</v>
       </c>
       <c r="U43" t="n">
-        <v>177.3190293564909</v>
+        <v>174.0835851199944</v>
       </c>
       <c r="V43" t="n">
-        <v>143.137643323828</v>
+        <v>139.9021990873316</v>
       </c>
       <c r="W43" t="n">
-        <v>177.522998336591</v>
+        <v>174.2875541000946</v>
       </c>
       <c r="X43" t="n">
-        <v>116.7096553890372</v>
+        <v>113.4742111525407</v>
       </c>
       <c r="Y43" t="n">
-        <v>109.5846533520948</v>
+        <v>106.3492091155983</v>
       </c>
     </row>
     <row r="44">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>321235.7536087034</v>
+        <v>317557.6312347343</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>394453.2317609262</v>
+        <v>394855.7721012837</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>394453.2317609261</v>
+        <v>394855.7721012837</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>394453.2317609261</v>
+        <v>394855.7721012837</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>394453.2317609261</v>
+        <v>394855.7721012837</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>389948.4893581561</v>
+        <v>390414.8661301639</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>439007.5556853758</v>
+        <v>439228.551806413</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>439007.5556853758</v>
+        <v>439228.5518064129</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>439007.5556853758</v>
+        <v>439228.551806413</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>439007.5556979525</v>
+        <v>439228.551806413</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>411409.3779990601</v>
+        <v>414756.1215172919</v>
       </c>
     </row>
     <row r="16">
@@ -26264,43 +26264,43 @@
         <v>921685.881056668</v>
       </c>
       <c r="C2" t="n">
+        <v>921685.8810566681</v>
+      </c>
+      <c r="D2" t="n">
         <v>921685.881056668</v>
       </c>
-      <c r="D2" t="n">
-        <v>921685.8810566681</v>
-      </c>
       <c r="E2" t="n">
-        <v>330390.7560075315</v>
+        <v>322218.0987575768</v>
       </c>
       <c r="F2" t="n">
-        <v>493636.2505623399</v>
+        <v>494572.7408805408</v>
       </c>
       <c r="G2" t="n">
-        <v>493636.2505623398</v>
+        <v>494572.7408805405</v>
       </c>
       <c r="H2" t="n">
-        <v>493636.2505623398</v>
+        <v>494572.7408805406</v>
       </c>
       <c r="I2" t="n">
-        <v>493636.2505623398</v>
+        <v>494572.7408805407</v>
       </c>
       <c r="J2" t="n">
-        <v>483188.1311753273</v>
+        <v>484241.1913958334</v>
       </c>
       <c r="K2" t="n">
-        <v>604240.5078046521</v>
+        <v>604801.280271327</v>
       </c>
       <c r="L2" t="n">
-        <v>604240.507804652</v>
+        <v>604801.2802713269</v>
       </c>
       <c r="M2" t="n">
-        <v>604240.507804652</v>
+        <v>604801.2802713269</v>
       </c>
       <c r="N2" t="n">
-        <v>604240.5078155356</v>
+        <v>604801.2802713269</v>
       </c>
       <c r="O2" t="n">
-        <v>534508.9771145713</v>
+        <v>542703.0631879219</v>
       </c>
       <c r="P2" t="n">
         <v>241891.6624457544</v>
@@ -26322,10 +26322,10 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>25600</v>
+        <v>23162.22005967057</v>
       </c>
       <c r="F3" t="n">
-        <v>48800</v>
+        <v>51525.12403366765</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -26337,10 +26337,10 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>22400</v>
+        <v>19992.18224746441</v>
       </c>
       <c r="K3" t="n">
-        <v>87200</v>
+        <v>89788.35538919717</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -26374,37 +26374,37 @@
         <v>467615.9599317312</v>
       </c>
       <c r="E4" t="n">
-        <v>188508.2893103003</v>
+        <v>184492.6945600646</v>
       </c>
       <c r="F4" t="n">
-        <v>268680.0047008537</v>
+        <v>269137.2732849513</v>
       </c>
       <c r="G4" t="n">
-        <v>268680.0047008537</v>
+        <v>269137.2732849513</v>
       </c>
       <c r="H4" t="n">
-        <v>268680.0047008537</v>
+        <v>269137.2732849513</v>
       </c>
       <c r="I4" t="n">
-        <v>268680.0047008537</v>
+        <v>269137.2732849513</v>
       </c>
       <c r="J4" t="n">
-        <v>263576.3244278131</v>
+        <v>264092.5943250212</v>
       </c>
       <c r="K4" t="n">
-        <v>322232.5449425578</v>
+        <v>322503.3176792525</v>
       </c>
       <c r="L4" t="n">
-        <v>322232.5449425578</v>
+        <v>322503.3176792525</v>
       </c>
       <c r="M4" t="n">
-        <v>322232.5449425577</v>
+        <v>322503.3176792525</v>
       </c>
       <c r="N4" t="n">
-        <v>322232.5449490701</v>
+        <v>322503.3176792525</v>
       </c>
       <c r="O4" t="n">
-        <v>288544.3831098055</v>
+        <v>292518.7781685568</v>
       </c>
       <c r="P4" t="n">
         <v>144738.4206832074</v>
@@ -26426,37 +26426,37 @@
         <v>33627.6</v>
       </c>
       <c r="E5" t="n">
-        <v>2690.208</v>
+        <v>2434.030847745557</v>
       </c>
       <c r="F5" t="n">
-        <v>7818.417</v>
+        <v>7848.612913228564</v>
       </c>
       <c r="G5" t="n">
-        <v>7818.417</v>
+        <v>7848.612913228564</v>
       </c>
       <c r="H5" t="n">
-        <v>7818.417</v>
+        <v>7848.612913228564</v>
       </c>
       <c r="I5" t="n">
-        <v>7818.417</v>
+        <v>7848.612913228564</v>
       </c>
       <c r="J5" t="n">
-        <v>7482.141000000001</v>
+        <v>7515.485527185614</v>
       </c>
       <c r="K5" t="n">
-        <v>11517.453</v>
+        <v>11536.42502322063</v>
       </c>
       <c r="L5" t="n">
-        <v>11517.453</v>
+        <v>11536.42502322063</v>
       </c>
       <c r="M5" t="n">
-        <v>11517.453</v>
+        <v>11536.42502322063</v>
       </c>
       <c r="N5" t="n">
-        <v>11517.453</v>
+        <v>11536.42502322063</v>
       </c>
       <c r="O5" t="n">
-        <v>9163.521000000001</v>
+        <v>9435.521561518022</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -26472,43 +26472,43 @@
         <v>420442.3211249368</v>
       </c>
       <c r="C6" t="n">
+        <v>420442.3211249369</v>
+      </c>
+      <c r="D6" t="n">
         <v>420442.3211249368</v>
       </c>
-      <c r="D6" t="n">
-        <v>420442.3211249369</v>
-      </c>
       <c r="E6" t="n">
-        <v>113592.2586972312</v>
+        <v>112129.153290096</v>
       </c>
       <c r="F6" t="n">
-        <v>168337.8288614862</v>
+        <v>166061.7306486932</v>
       </c>
       <c r="G6" t="n">
-        <v>217137.8288614861</v>
+        <v>217586.8546823605</v>
       </c>
       <c r="H6" t="n">
-        <v>217137.8288614861</v>
+        <v>217586.8546823607</v>
       </c>
       <c r="I6" t="n">
-        <v>217137.8288614861</v>
+        <v>217586.8546823608</v>
       </c>
       <c r="J6" t="n">
-        <v>189729.6657475142</v>
+        <v>192640.9292961622</v>
       </c>
       <c r="K6" t="n">
-        <v>183290.5098620943</v>
+        <v>180973.1821796567</v>
       </c>
       <c r="L6" t="n">
-        <v>270490.5098620942</v>
+        <v>270761.5375688537</v>
       </c>
       <c r="M6" t="n">
-        <v>270490.5098620943</v>
+        <v>270761.5375688538</v>
       </c>
       <c r="N6" t="n">
-        <v>270490.5098664656</v>
+        <v>270761.5375688538</v>
       </c>
       <c r="O6" t="n">
-        <v>236801.0730047657</v>
+        <v>240748.7634578471</v>
       </c>
       <c r="P6" t="n">
         <v>97153.241762547</v>
@@ -26632,37 +26632,37 @@
         <v>400</v>
       </c>
       <c r="E2" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="F2" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G2" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H2" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I2" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J2" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="K2" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="L2" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="M2" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="N2" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="O2" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -26840,7 +26840,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -26849,10 +26849,10 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="F2" t="n">
-        <v>61</v>
+        <v>64.40640504208456</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -26861,28 +26861,28 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>28</v>
+        <v>24.99022780933052</v>
       </c>
       <c r="K2" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26892,13 +26892,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -26907,19 +26907,19 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -26931,10 +26931,10 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26944,49 +26944,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27081,10 +27081,10 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="K2" t="n">
-        <v>61</v>
+        <v>64.40640504208456</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -27096,10 +27096,10 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>28</v>
+        <v>24.99022780933052</v>
       </c>
       <c r="P2" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
     </row>
     <row r="3">
@@ -28012,31 +28012,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="C11" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="D11" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="E11" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="F11" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="G11" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="H11" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="I11" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="J11" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -28057,31 +28057,31 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="R11" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="S11" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="T11" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="U11" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="V11" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="W11" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="X11" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="Y11" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
     </row>
     <row r="12">
@@ -28091,40 +28091,40 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="C12" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="D12" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="E12" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="F12" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="G12" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="H12" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="I12" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="J12" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>21.30487222469803</v>
       </c>
       <c r="M12" t="n">
-        <v>23.54716981132075</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -28133,34 +28133,34 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="S12" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="T12" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="U12" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="V12" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="W12" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="X12" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="Y12" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
     </row>
     <row r="13">
@@ -28170,76 +28170,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="C13" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="D13" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="E13" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="F13" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="G13" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="H13" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="I13" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="J13" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="K13" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="L13" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="M13" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="N13" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="O13" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="P13" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="Q13" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="R13" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="S13" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="T13" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="U13" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="V13" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="W13" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="X13" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="Y13" t="n">
-        <v>32</v>
+        <v>28.95277507458822</v>
       </c>
     </row>
     <row r="14">
@@ -28249,31 +28249,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C14" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D14" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E14" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F14" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G14" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H14" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I14" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J14" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -28285,7 +28285,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -28294,31 +28294,31 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="R14" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S14" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T14" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U14" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V14" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W14" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X14" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y14" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="15">
@@ -28328,40 +28328,40 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C15" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D15" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E15" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F15" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G15" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H15" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I15" t="n">
-        <v>89.39663285141508</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J15" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>68.69826461415563</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -28370,34 +28370,34 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S15" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T15" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U15" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V15" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W15" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X15" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y15" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="16">
@@ -28407,76 +28407,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J16" t="n">
-        <v>93.00000000000001</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="M16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="N16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="O16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="P16" t="n">
-        <v>4.815948629165844</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Q16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="R16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="17">
@@ -28486,31 +28486,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C17" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D17" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E17" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F17" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G17" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H17" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I17" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J17" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -28531,31 +28531,31 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="R17" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S17" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T17" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U17" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V17" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W17" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X17" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y17" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="18">
@@ -28565,37 +28565,37 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C18" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D18" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E18" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F18" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G18" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H18" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I18" t="n">
-        <v>93</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J18" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K18" t="n">
-        <v>68.43396226415095</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -28607,34 +28607,34 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Q18" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S18" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T18" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U18" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V18" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W18" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X18" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y18" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="19">
@@ -28644,76 +28644,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="L19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="M19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="N19" t="n">
-        <v>93</v>
+        <v>56.79206289751328</v>
       </c>
       <c r="O19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="P19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Q19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="R19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="20">
@@ -28723,31 +28723,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C20" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D20" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E20" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F20" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G20" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H20" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I20" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J20" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -28768,31 +28768,31 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="R20" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S20" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T20" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U20" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V20" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W20" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X20" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y20" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="21">
@@ -28802,34 +28802,34 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C21" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D21" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E21" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F21" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G21" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H21" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I21" t="n">
-        <v>93</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J21" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K21" t="n">
-        <v>68.43396226415095</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -28838,40 +28838,40 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S21" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T21" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U21" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V21" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W21" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X21" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y21" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="22">
@@ -28881,76 +28881,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J22" t="n">
-        <v>92.99999999999999</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="L22" t="n">
-        <v>93</v>
+        <v>56.79206289751328</v>
       </c>
       <c r="M22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="N22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="O22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="P22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Q22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="R22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="23">
@@ -28960,31 +28960,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C23" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D23" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E23" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F23" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G23" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H23" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I23" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J23" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -29005,31 +29005,31 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="R23" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S23" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T23" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U23" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V23" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W23" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X23" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y23" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="24">
@@ -29039,34 +29039,34 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C24" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D24" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E24" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F24" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G24" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H24" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I24" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J24" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K24" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -29075,10 +29075,10 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="O24" t="n">
-        <v>68.43396226415095</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -29087,28 +29087,28 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S24" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T24" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U24" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V24" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W24" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X24" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y24" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="25">
@@ -29118,76 +29118,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="L25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="M25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="N25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="O25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="P25" t="n">
-        <v>93</v>
+        <v>56.98869959386986</v>
       </c>
       <c r="Q25" t="n">
-        <v>93</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="26">
@@ -29197,31 +29197,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="C26" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="D26" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="E26" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="F26" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="G26" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="H26" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="I26" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J26" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -29242,31 +29242,31 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>76.47738693467336</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="R26" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="S26" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="T26" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="U26" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="V26" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="W26" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="X26" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="Y26" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
     </row>
     <row r="27">
@@ -29276,37 +29276,37 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="C27" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="D27" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="E27" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="F27" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="G27" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="H27" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="I27" t="n">
-        <v>89.00000000000001</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J27" t="n">
-        <v>89</v>
+        <v>65.78242794727026</v>
       </c>
       <c r="K27" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -29315,7 +29315,7 @@
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -29324,28 +29324,28 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="S27" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="T27" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="U27" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="V27" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="W27" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="X27" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="Y27" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
     </row>
     <row r="28">
@@ -29355,76 +29355,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="C28" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="D28" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="E28" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="F28" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="G28" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="H28" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="I28" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J28" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="K28" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="L28" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="M28" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="N28" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="O28" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="P28" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="Q28" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="R28" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="S28" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="T28" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="U28" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="V28" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="W28" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="X28" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="Y28" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
     </row>
     <row r="29">
@@ -29434,31 +29434,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="C29" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="D29" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="E29" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="F29" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="G29" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="H29" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="I29" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="J29" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -29479,31 +29479,31 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="R29" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="S29" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="T29" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="U29" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="V29" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="W29" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="X29" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="Y29" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
     </row>
     <row r="30">
@@ -29513,22 +29513,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="C30" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="D30" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="E30" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="F30" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="G30" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="H30" t="n">
         <v>112.2354442364965</v>
@@ -29540,49 +29540,49 @@
         <v>126.8376266666667</v>
       </c>
       <c r="K30" t="n">
-        <v>137.0000000000004</v>
+        <v>92.65603387457384</v>
       </c>
       <c r="L30" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>137.225672045827</v>
       </c>
       <c r="P30" t="n">
         <v>133.9744074143302</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>137.225672045827</v>
       </c>
       <c r="R30" t="n">
-        <v>100.1578341526431</v>
+        <v>137.225672045827</v>
       </c>
       <c r="S30" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="T30" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="U30" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="V30" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="W30" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="X30" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="Y30" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
     </row>
     <row r="31">
@@ -29592,31 +29592,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="C31" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="D31" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="E31" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="F31" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="G31" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="H31" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="I31" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="J31" t="n">
-        <v>111.2974604516679</v>
+        <v>126.9954214393961</v>
       </c>
       <c r="K31" t="n">
         <v>129.0132581705354</v>
@@ -29634,34 +29634,34 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>137.0000000000001</v>
+        <v>137.225672045827</v>
       </c>
       <c r="Q31" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="R31" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="S31" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="T31" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="U31" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="V31" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="W31" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="X31" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="Y31" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
     </row>
     <row r="32">
@@ -29671,31 +29671,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="C32" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="D32" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="E32" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="F32" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="G32" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="H32" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="I32" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="J32" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -29716,31 +29716,31 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="R32" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="S32" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="T32" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="U32" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="V32" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="W32" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="X32" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="Y32" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
     </row>
     <row r="33">
@@ -29750,25 +29750,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="C33" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="D33" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="E33" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="F33" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="G33" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="H33" t="n">
-        <v>112.2354442364966</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I33" t="n">
         <v>99.52238</v>
@@ -29777,49 +29777,49 @@
         <v>126.8376266666667</v>
       </c>
       <c r="K33" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O33" t="n">
-        <v>91.27219585770244</v>
+        <v>137.225672045827</v>
       </c>
       <c r="P33" t="n">
-        <v>133.9744074143303</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>92.65603387457411</v>
       </c>
       <c r="R33" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="S33" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="T33" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="U33" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="V33" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="W33" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="X33" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="Y33" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
     </row>
     <row r="34">
@@ -29829,28 +29829,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="C34" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="D34" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="E34" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="F34" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="G34" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="H34" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="I34" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="J34" t="n">
         <v>126.9954214393961</v>
@@ -29871,34 +29871,34 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>137.0000000000001</v>
+        <v>137.225672045827</v>
       </c>
       <c r="Q34" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="R34" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="S34" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="T34" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="U34" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="V34" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="W34" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="X34" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="Y34" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
     </row>
     <row r="35">
@@ -29908,31 +29908,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="C35" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="D35" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="E35" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="F35" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="G35" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="H35" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="I35" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="J35" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -29953,31 +29953,31 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="R35" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="S35" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="T35" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="U35" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="V35" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="W35" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="X35" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="Y35" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
     </row>
     <row r="36">
@@ -29987,76 +29987,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="C36" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="D36" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="E36" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="F36" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="G36" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="H36" t="n">
         <v>112.2354442364965</v>
       </c>
       <c r="I36" t="n">
-        <v>89.39663285141508</v>
+        <v>99.52238</v>
       </c>
       <c r="J36" t="n">
-        <v>0.7465913262578567</v>
+        <v>126.8376266666667</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="M36" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="N36" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O36" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="P36" t="n">
-        <v>133.9744074143303</v>
+        <v>89.40476924307686</v>
       </c>
       <c r="Q36" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>100.1578341526431</v>
+        <v>137.225672045827</v>
       </c>
       <c r="S36" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="T36" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="U36" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="V36" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="W36" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="X36" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="Y36" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
     </row>
     <row r="37">
@@ -30066,34 +30066,34 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="C37" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="D37" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="E37" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="F37" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="G37" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="H37" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="I37" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="J37" t="n">
         <v>126.9954214393961</v>
       </c>
       <c r="K37" t="n">
-        <v>111.9316129133629</v>
+        <v>129.0132581705354</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -30108,34 +30108,34 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>137.0000000000001</v>
+        <v>137.225672045827</v>
       </c>
       <c r="Q37" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="R37" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="S37" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="T37" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="U37" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="V37" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="W37" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="X37" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="Y37" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
     </row>
     <row r="38">
@@ -30145,31 +30145,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="C38" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="D38" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="E38" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="F38" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="G38" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="H38" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="I38" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="J38" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -30190,31 +30190,31 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="R38" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="S38" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="T38" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="U38" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="V38" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="W38" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="X38" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="Y38" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
     </row>
     <row r="39">
@@ -30224,76 +30224,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="C39" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="D39" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="E39" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="F39" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="G39" t="n">
-        <v>137.0000002281692</v>
+        <v>137.225672045827</v>
       </c>
       <c r="H39" t="n">
-        <v>112.2354442364966</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I39" t="n">
-        <v>99.52238000000006</v>
+        <v>99.52238</v>
       </c>
       <c r="J39" t="n">
         <v>126.8376266666667</v>
       </c>
       <c r="K39" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>137.225672045827</v>
       </c>
       <c r="M39" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O39" t="n">
-        <v>128.1143614768905</v>
+        <v>137.225672045827</v>
       </c>
       <c r="P39" t="n">
-        <v>133.9744074143302</v>
+        <v>89.4047692430763</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>137.225672045827</v>
       </c>
       <c r="R39" t="n">
-        <v>100.1578341526431</v>
+        <v>137.225672045827</v>
       </c>
       <c r="S39" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="T39" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="U39" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="V39" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="W39" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="X39" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="Y39" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
     </row>
     <row r="40">
@@ -30303,28 +30303,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="C40" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="D40" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="E40" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="F40" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="G40" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="H40" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="I40" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="J40" t="n">
         <v>126.9954214393961</v>
@@ -30345,34 +30345,34 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="Q40" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="R40" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="S40" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="T40" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="U40" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="V40" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="W40" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="X40" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="Y40" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
     </row>
     <row r="41">
@@ -30382,31 +30382,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="C41" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="D41" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="E41" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="F41" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="G41" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="H41" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I41" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="J41" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -30427,31 +30427,31 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="R41" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="S41" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="T41" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="U41" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="V41" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="W41" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="X41" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="Y41" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
     </row>
     <row r="42">
@@ -30461,76 +30461,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="C42" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="D42" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="E42" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="F42" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="G42" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="H42" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I42" t="n">
-        <v>89.39663285141508</v>
+        <v>99.52238</v>
       </c>
       <c r="J42" t="n">
-        <v>28.44553299594178</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="M42" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>109</v>
+        <v>24.79067432035411</v>
       </c>
       <c r="O42" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="P42" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="R42" t="n">
         <v>100.1578341526431</v>
       </c>
       <c r="S42" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="T42" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="U42" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="V42" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="W42" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="X42" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="Y42" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
     </row>
     <row r="43">
@@ -30540,34 +30540,34 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="C43" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="D43" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="E43" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="F43" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="G43" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="H43" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I43" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="J43" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="K43" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -30582,34 +30582,34 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="Q43" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="R43" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="S43" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="T43" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="U43" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="V43" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="W43" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="X43" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="Y43" t="n">
-        <v>109</v>
+        <v>112.2354442364965</v>
       </c>
     </row>
     <row r="44">
